--- a/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_44.xlsx
+++ b/model/Outputs/11. Interest rate/40/Output Files/0.1/Output_9_44.xlsx
@@ -496,7 +496,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5439522.79971191</v>
+        <v>5479459.97848699</v>
       </c>
     </row>
     <row r="7">
@@ -556,7 +556,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>42272929.04492003</v>
+        <v>42272929.04492002</v>
       </c>
     </row>
   </sheetData>
@@ -657,43 +657,43 @@
         <v>81.99931295557451</v>
       </c>
       <c r="C2" t="n">
-        <v>49.47457824299391</v>
+        <v>449.4745782429939</v>
       </c>
       <c r="D2" t="n">
-        <v>410.3391557398498</v>
+        <v>10.33915573984979</v>
       </c>
       <c r="E2" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F2" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G2" t="n">
-        <v>3.75737228701621</v>
+        <v>96.3670051614515</v>
       </c>
       <c r="H2" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J2" t="n">
-        <v>418.7382696589336</v>
+        <v>797.8013999999999</v>
       </c>
       <c r="K2" t="n">
-        <v>97.12488247690067</v>
+        <v>97.12488247690055</v>
       </c>
       <c r="L2" t="n">
-        <v>216.0296191332224</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>297.9910820919849</v>
+        <v>814</v>
       </c>
       <c r="N2" t="n">
-        <v>194.5855355810472</v>
+        <v>329.5431064651884</v>
       </c>
       <c r="O2" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>814</v>
@@ -702,7 +702,7 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S2" t="n">
         <v>94.84816780232291</v>
@@ -717,13 +717,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W2" t="n">
-        <v>331.942867366362</v>
+        <v>238.3734759809475</v>
       </c>
       <c r="X2" t="n">
         <v>592.2818334606677</v>
       </c>
       <c r="Y2" t="n">
-        <v>511.3174326828064</v>
+        <v>111.3174326828064</v>
       </c>
     </row>
     <row r="3">
@@ -733,10 +733,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
@@ -751,7 +751,7 @@
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>332.1680871864211</v>
+        <v>0</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -778,13 +778,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>141.0009805506751</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>147.2737972923793</v>
+        <v>547.2737972923793</v>
       </c>
       <c r="S3" t="n">
-        <v>66.5639999646113</v>
+        <v>163.1897119025149</v>
       </c>
       <c r="T3" t="n">
         <v>5.357765217513816</v>
@@ -842,7 +842,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M4" t="n">
         <v>120.6316114025499</v>
@@ -860,7 +860,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R4" t="n">
-        <v>320.939678284696</v>
+        <v>297.3920501269219</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -897,28 +897,28 @@
         <v>49.47457824299391</v>
       </c>
       <c r="D5" t="n">
-        <v>10.33915573984979</v>
+        <v>410.3391557398498</v>
       </c>
       <c r="E5" t="n">
-        <v>4.363289606868648</v>
+        <v>404.3632896068686</v>
       </c>
       <c r="F5" t="n">
-        <v>348.3778604107411</v>
+        <v>404.8896287080119</v>
       </c>
       <c r="G5" t="n">
         <v>3.75737228701621</v>
       </c>
       <c r="H5" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I5" t="n">
         <v>150.0811596826846</v>
       </c>
       <c r="J5" t="n">
-        <v>418.7382696589372</v>
+        <v>797.801400000028</v>
       </c>
       <c r="K5" t="n">
-        <v>814</v>
+        <v>748.0913712690282</v>
       </c>
       <c r="L5" t="n">
         <v>814</v>
@@ -927,7 +927,7 @@
         <v>297.9910820919849</v>
       </c>
       <c r="N5" t="n">
-        <v>507.7400371911697</v>
+        <v>194.5855355810509</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -942,10 +942,10 @@
         <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>494.8481678023229</v>
+        <v>438.3363995050528</v>
       </c>
       <c r="T5" t="n">
-        <v>586.6755817285639</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U5" t="n">
         <v>249.2212965486107</v>
@@ -970,19 +970,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>148.6880250402008</v>
       </c>
       <c r="C6" t="n">
-        <v>0</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D6" t="n">
-        <v>175.4172848236332</v>
+        <v>347.9376868977026</v>
       </c>
       <c r="E6" t="n">
-        <v>342.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>339.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1082,7 +1082,7 @@
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>114.9691617061026</v>
+        <v>114.9691617061037</v>
       </c>
       <c r="N7" t="n">
         <v>171.1850752716849</v>
@@ -1137,28 +1137,28 @@
         <v>10.33915573984979</v>
       </c>
       <c r="E8" t="n">
-        <v>404.3632896068686</v>
+        <v>4.363289606868648</v>
       </c>
       <c r="F8" t="n">
         <v>4.889628708011855</v>
       </c>
       <c r="G8" t="n">
-        <v>403.7573722870162</v>
+        <v>3.75737228701621</v>
       </c>
       <c r="H8" t="n">
-        <v>408.0096587035274</v>
+        <v>8.009658703527407</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>150.0811596826846</v>
       </c>
       <c r="J8" t="n">
         <v>418.7382696589336</v>
       </c>
       <c r="K8" t="n">
-        <v>313.1545016101269</v>
+        <v>97.12488247690067</v>
       </c>
       <c r="L8" t="n">
-        <v>814</v>
+        <v>216.0296191332224</v>
       </c>
       <c r="M8" t="n">
         <v>297.9910820919849</v>
@@ -1167,7 +1167,7 @@
         <v>194.5855355810472</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>814</v>
       </c>
       <c r="P8" t="n">
         <v>814</v>
@@ -1176,13 +1176,13 @@
         <v>370.9706110579117</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>250.8785988282945</v>
       </c>
       <c r="S8" t="n">
-        <v>494.8481678023229</v>
+        <v>187.4578006767583</v>
       </c>
       <c r="T8" t="n">
-        <v>280.2449731139786</v>
+        <v>186.6755817285639</v>
       </c>
       <c r="U8" t="n">
         <v>249.2212965486107</v>
@@ -1191,13 +1191,13 @@
         <v>229.8510241668239</v>
       </c>
       <c r="W8" t="n">
-        <v>238.3734759809475</v>
+        <v>638.3734759809475</v>
       </c>
       <c r="X8" t="n">
-        <v>192.2818334606677</v>
+        <v>592.2818334606677</v>
       </c>
       <c r="Y8" t="n">
-        <v>111.3174326828064</v>
+        <v>511.3174326828064</v>
       </c>
     </row>
     <row r="9">
@@ -1207,13 +1207,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>384.5565566463266</v>
+        <v>0</v>
       </c>
       <c r="C9" t="n">
-        <v>73.16906773709616</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>0</v>
+        <v>58.33423161728842</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
@@ -1276,7 +1276,7 @@
         <v>419.8627394453875</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>399.3913927661343</v>
       </c>
     </row>
     <row r="10">
@@ -1316,10 +1316,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>120.6316114025499</v>
+        <v>114.9691617060968</v>
       </c>
       <c r="N10" t="n">
         <v>171.1850752716849</v>
@@ -1334,7 +1334,7 @@
         <v>325.839266425598</v>
       </c>
       <c r="R10" t="n">
-        <v>297.3920501269282</v>
+        <v>326.6021279811511</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -1368,22 +1368,22 @@
         <v>256.9993129555745</v>
       </c>
       <c r="C11" t="n">
-        <v>224.4745782429939</v>
+        <v>101.9886654575968</v>
       </c>
       <c r="D11" t="n">
-        <v>149.9284964306882</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>179.3632896068686</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>179.8896287080119</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -1416,7 +1416,7 @@
         <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>269.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
         <v>361.6755817285639</v>
@@ -1568,10 +1568,10 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="n">
         <v>340.7767994885277</v>
-      </c>
-      <c r="R13" t="n">
-        <v>0</v>
       </c>
       <c r="S13" t="n">
         <v>0</v>
@@ -1611,16 +1611,16 @@
         <v>159.3391557398498</v>
       </c>
       <c r="E14" t="n">
-        <v>153.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>71.22605108397006</v>
+        <v>67.57968198731129</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>157.0096587035274</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -1796,19 +1796,19 @@
         <v>0</v>
       </c>
       <c r="N16" t="n">
-        <v>139.1349830766931</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>389.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P16" t="n">
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>52.97841917455702</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>475.6021279811511</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -1854,7 +1854,7 @@
         <v>125.8896287080119</v>
       </c>
       <c r="G17" t="n">
-        <v>124.7573722870162</v>
+        <v>124.3267636724302</v>
       </c>
       <c r="H17" t="n">
         <v>129.0096587035274</v>
@@ -1890,7 +1890,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T17" t="n">
         <v>307.6755817285639</v>
@@ -2039,13 +2039,13 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="Q19" t="n">
-        <v>338.6387678008247</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R19" t="n">
-        <v>447.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
         <v>0</v>
@@ -2127,7 +2127,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>215.4175591877372</v>
+        <v>215.8481678023229</v>
       </c>
       <c r="T20" t="n">
         <v>307.6755817285639</v>
@@ -2139,7 +2139,7 @@
         <v>350.8510241668239</v>
       </c>
       <c r="W20" t="n">
-        <v>359.3734759809475</v>
+        <v>358.9428673663618</v>
       </c>
       <c r="X20" t="n">
         <v>313.2818334606677</v>
@@ -2273,16 +2273,16 @@
         <v>0</v>
       </c>
       <c r="O22" t="n">
-        <v>338.6387678008247</v>
+        <v>0</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>446.839266425598</v>
       </c>
       <c r="R22" t="n">
-        <v>447.6021279811511</v>
+        <v>339.4016293563777</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -2364,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>215.8481678023229</v>
+        <v>215.4175591877372</v>
       </c>
       <c r="T23" t="n">
         <v>307.6755817285639</v>
@@ -2376,7 +2376,7 @@
         <v>350.8510241668239</v>
       </c>
       <c r="W23" t="n">
-        <v>358.9428673663618</v>
+        <v>359.3734759809475</v>
       </c>
       <c r="X23" t="n">
         <v>313.2818334606677</v>
@@ -2471,16 +2471,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>8.113800337078658</v>
+        <v>0</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>6.53621805555548</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
-        <v>1.98090483695654</v>
+        <v>0</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -2498,31 +2498,31 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>9.520773801143037</v>
+        <v>0</v>
       </c>
       <c r="L25" t="n">
         <v>144.5476281577792</v>
       </c>
       <c r="M25" t="n">
-        <v>207.0936732651854</v>
+        <v>241.6316114025499</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>292.1850752716849</v>
       </c>
       <c r="O25" t="n">
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>408.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
         <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>24.50310124710636</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>83.37347970285543</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -2556,19 +2556,19 @@
         <v>224.4745782429939</v>
       </c>
       <c r="D26" t="n">
-        <v>185.3391557398498</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>71.36490157718852</v>
       </c>
       <c r="F26" t="n">
         <v>179.8896287080119</v>
       </c>
       <c r="G26" t="n">
-        <v>178.7573722870162</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -2607,10 +2607,10 @@
         <v>361.6755817285639</v>
       </c>
       <c r="U26" t="n">
-        <v>67.01360287942316</v>
+        <v>424.2212965486107</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>404.8510241668239</v>
       </c>
       <c r="W26" t="n">
         <v>413.3734759809475</v>
@@ -2619,7 +2619,7 @@
         <v>367.2818334606677</v>
       </c>
       <c r="Y26" t="n">
-        <v>286.3174326828064</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -2741,7 +2741,7 @@
         <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>203.4033197856722</v>
       </c>
       <c r="N28" t="n">
         <v>0</v>
@@ -2753,13 +2753,13 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>342.1496093272373</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
         <v>0</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>137.3734797028554</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -2771,7 +2771,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>1.372809838709685</v>
       </c>
       <c r="X28" t="n">
         <v>0</v>
@@ -2787,10 +2787,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>36.59725481811878</v>
+        <v>256.9993129555745</v>
       </c>
       <c r="C29" t="n">
-        <v>224.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D29" t="n">
         <v>185.3391557398498</v>
@@ -2805,7 +2805,7 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>4.07252010553818</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>340.7767994885277</v>
       </c>
       <c r="O31" t="n">
         <v>0</v>
       </c>
       <c r="P31" t="n">
-        <v>340.7767994885277</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
         <v>0</v>
@@ -3051,19 +3051,19 @@
         <v>377.7382696589747</v>
       </c>
       <c r="K32" t="n">
-        <v>727.1079320760099</v>
+        <v>773</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>727.1079320760826</v>
       </c>
       <c r="M32" t="n">
         <v>256.9910820920259</v>
       </c>
       <c r="N32" t="n">
-        <v>551.2932893429752</v>
+        <v>153.5855355810884</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>397.7077537618853</v>
       </c>
       <c r="P32" t="n">
         <v>0</v>
@@ -3221,13 +3221,13 @@
         <v>0</v>
       </c>
       <c r="O34" t="n">
-        <v>0</v>
+        <v>349.445564079015</v>
       </c>
       <c r="P34" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>37.06842018211179</v>
+        <v>84.07075343137427</v>
       </c>
       <c r="R34" t="n">
         <v>435.6021279811511</v>
@@ -3279,7 +3279,7 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H35" t="n">
-        <v>125.4662500889416</v>
+        <v>117.0096587035274</v>
       </c>
       <c r="I35" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
         <v>377.738269658982</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760351</v>
+        <v>10.23281455290589</v>
       </c>
       <c r="L35" t="n">
         <v>773</v>
@@ -3300,16 +3300,16 @@
         <v>153.5855355810957</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>341.5828712849043</v>
       </c>
       <c r="Q35" t="n">
-        <v>727.6783648198607</v>
+        <v>329.9706110579601</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S35" t="n">
         <v>203.8481678023229</v>
@@ -3449,28 +3449,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>0</v>
+        <v>132.5476281577792</v>
       </c>
       <c r="M37" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O37" t="n">
-        <v>0</v>
+        <v>226.7541306595264</v>
       </c>
       <c r="P37" t="n">
-        <v>396.4478973282775</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>109.2047614405202</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
-        <v>0</v>
+        <v>71.37347970285543</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -3516,7 +3516,7 @@
         <v>112.7573722870162</v>
       </c>
       <c r="H38" t="n">
-        <v>125.4662500889416</v>
+        <v>117.0096587035274</v>
       </c>
       <c r="I38" t="n">
         <v>0</v>
@@ -3525,7 +3525,7 @@
         <v>377.7382696589893</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762731</v>
+        <v>56.12488247690057</v>
       </c>
       <c r="L38" t="n">
         <v>773</v>
@@ -3537,16 +3537,16 @@
         <v>153.5855355811029</v>
       </c>
       <c r="O38" t="n">
-        <v>397.7077537619086</v>
+        <v>773.0000000000557</v>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>295.6908033608921</v>
       </c>
       <c r="Q38" t="n">
         <v>329.9706110579674</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>8.456591385414804</v>
       </c>
       <c r="S38" t="n">
         <v>203.8481678023229</v>
@@ -3689,22 +3689,22 @@
         <v>132.5476281577792</v>
       </c>
       <c r="M40" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N40" t="n">
-        <v>71.33707795008732</v>
+        <v>0</v>
       </c>
       <c r="O40" t="n">
         <v>0</v>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>301.7315509081631</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R40" t="n">
-        <v>435.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>71.37347970285543</v>
@@ -3735,25 +3735,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>268.9993129555745</v>
+        <v>0</v>
       </c>
       <c r="C41" t="n">
         <v>236.4745782429939</v>
       </c>
       <c r="D41" t="n">
-        <v>197.3391557398498</v>
+        <v>113.9364105579687</v>
       </c>
       <c r="E41" t="n">
-        <v>191.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>191.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>195.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -3783,22 +3783,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>37.87859882829446</v>
       </c>
       <c r="S41" t="n">
         <v>281.8481678023229</v>
       </c>
       <c r="T41" t="n">
-        <v>323.1140455487659</v>
+        <v>373.6755817285639</v>
       </c>
       <c r="U41" t="n">
         <v>436.2212965486107</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>416.8510241668239</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>425.3734759809475</v>
       </c>
       <c r="X41" t="n">
         <v>379.2818334606677</v>
@@ -3877,7 +3877,7 @@
         <v>201.5106671915202</v>
       </c>
       <c r="W42" t="n">
-        <v>0</v>
+        <v>81.90670016750896</v>
       </c>
       <c r="X42" t="n">
         <v>206.8627394453875</v>
@@ -3941,7 +3941,7 @@
         <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>144.701836962599</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -3972,10 +3972,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>142.4109888009625</v>
+        <v>294.9993129555745</v>
       </c>
       <c r="C44" t="n">
-        <v>0</v>
+        <v>262.4745782429939</v>
       </c>
       <c r="D44" t="n">
         <v>0</v>
@@ -4023,7 +4023,7 @@
         <v>63.87859882829446</v>
       </c>
       <c r="S44" t="n">
-        <v>307.8481678023229</v>
+        <v>0</v>
       </c>
       <c r="T44" t="n">
         <v>399.6755817285639</v>
@@ -4038,7 +4038,7 @@
         <v>451.3734759809475</v>
       </c>
       <c r="X44" t="n">
-        <v>405.2818334606677</v>
+        <v>298.0670988653846</v>
       </c>
       <c r="Y44" t="n">
         <v>324.3174326828064</v>
@@ -4054,16 +4054,16 @@
         <v>197.5565566463266</v>
       </c>
       <c r="C45" t="n">
-        <v>108.647691156336</v>
+        <v>174.0999124455193</v>
       </c>
       <c r="D45" t="n">
-        <v>0</v>
+        <v>160.9376868977026</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>155.6720972219126</v>
       </c>
       <c r="F45" t="n">
-        <v>0</v>
+        <v>152.6362423378769</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>0</v>
       </c>
       <c r="I45" t="n">
-        <v>0</v>
+        <v>30.12638589134853</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -4099,10 +4099,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>360.2737972923793</v>
+        <v>324.1087118377447</v>
       </c>
       <c r="S45" t="n">
-        <v>279.5639999646113</v>
+        <v>0</v>
       </c>
       <c r="T45" t="n">
         <v>218.3577652175138</v>
@@ -4114,7 +4114,7 @@
         <v>227.5106671915202</v>
       </c>
       <c r="W45" t="n">
-        <v>245.3731429098285</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>232.8627394453875</v>
@@ -4148,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>41.77112610161862</v>
+        <v>0</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -4184,13 +4184,13 @@
         <v>0</v>
       </c>
       <c r="T46" t="n">
-        <v>0</v>
+        <v>23.02456650625771</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>0</v>
+        <v>12.17031021621619</v>
       </c>
       <c r="W46" t="n">
         <v>39.37280983870968</v>
@@ -4297,43 +4297,43 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>954.8509932204727</v>
+        <v>1199.993207924634</v>
       </c>
       <c r="C2" t="n">
-        <v>904.876671762903</v>
+        <v>745.9784824266604</v>
       </c>
       <c r="D2" t="n">
-        <v>490.392676066085</v>
+        <v>735.5348907702465</v>
       </c>
       <c r="E2" t="n">
-        <v>485.9853128268237</v>
+        <v>327.0871234905812</v>
       </c>
       <c r="F2" t="n">
-        <v>481.046293929842</v>
+        <v>322.1481045935996</v>
       </c>
       <c r="G2" t="n">
-        <v>477.2509683874014</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H2" t="n">
-        <v>65.12</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I2" t="n">
         <v>65.12</v>
       </c>
       <c r="J2" t="n">
-        <v>448.0120508495621</v>
+        <v>65.12</v>
       </c>
       <c r="K2" t="n">
-        <v>1155.766108953703</v>
+        <v>772.8740581041409</v>
       </c>
       <c r="L2" t="n">
-        <v>1743.414372455498</v>
+        <v>1578.734058104141</v>
       </c>
       <c r="M2" t="n">
-        <v>2248.273279433291</v>
+        <v>1562.371835881919</v>
       </c>
       <c r="N2" t="n">
-        <v>2857.58223339183</v>
+        <v>2035.360011169607</v>
       </c>
       <c r="O2" t="n">
         <v>2841.220011169607</v>
@@ -4345,28 +4345,28 @@
         <v>3256</v>
       </c>
       <c r="R2" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S2" t="n">
-        <v>3160.193769896644</v>
+        <v>2906.781043807457</v>
       </c>
       <c r="T2" t="n">
-        <v>2971.632576231427</v>
+        <v>2718.219850142241</v>
       </c>
       <c r="U2" t="n">
-        <v>2719.893892848992</v>
+        <v>2466.481166759806</v>
       </c>
       <c r="V2" t="n">
-        <v>2487.721141165332</v>
+        <v>2234.308415076146</v>
       </c>
       <c r="W2" t="n">
-        <v>2152.425315542744</v>
+        <v>1993.527126206502</v>
       </c>
       <c r="X2" t="n">
-        <v>1554.160837299645</v>
+        <v>1395.262647963403</v>
       </c>
       <c r="Y2" t="n">
-        <v>1037.678582064487</v>
+        <v>1282.820796768649</v>
       </c>
     </row>
     <row r="3">
@@ -4376,22 +4376,22 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>400.6433203903244</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="C3" t="n">
-        <v>400.6433203903244</v>
+        <v>65.12</v>
       </c>
       <c r="D3" t="n">
-        <v>400.6433203903244</v>
+        <v>65.12</v>
       </c>
       <c r="E3" t="n">
-        <v>400.6433203903244</v>
+        <v>65.12</v>
       </c>
       <c r="F3" t="n">
-        <v>400.6433203903244</v>
+        <v>65.12</v>
       </c>
       <c r="G3" t="n">
-        <v>400.6433203903244</v>
+        <v>65.12</v>
       </c>
       <c r="H3" t="n">
         <v>65.12</v>
@@ -4421,31 +4421,31 @@
         <v>1220.552420368536</v>
       </c>
       <c r="Q3" t="n">
-        <v>1078.127187489066</v>
+        <v>1220.552420368536</v>
       </c>
       <c r="R3" t="n">
-        <v>929.3657760826221</v>
+        <v>667.7506049216878</v>
       </c>
       <c r="S3" t="n">
-        <v>862.1294124820047</v>
+        <v>502.9125120908647</v>
       </c>
       <c r="T3" t="n">
-        <v>856.7175284239099</v>
+        <v>497.50062803277</v>
       </c>
       <c r="U3" t="n">
-        <v>856.5050438176606</v>
+        <v>497.2881434265207</v>
       </c>
       <c r="V3" t="n">
-        <v>841.8478042302665</v>
+        <v>482.6309038391266</v>
       </c>
       <c r="W3" t="n">
-        <v>809.1476598769044</v>
+        <v>449.9307594857645</v>
       </c>
       <c r="X3" t="n">
-        <v>789.0842866997452</v>
+        <v>429.8673863086054</v>
       </c>
       <c r="Y3" t="n">
-        <v>789.0842866997452</v>
+        <v>429.8673863086054</v>
       </c>
     </row>
     <row r="4">
@@ -4455,52 +4455,52 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>982.2165206090069</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="C4" t="n">
-        <v>1108.218526427443</v>
+        <v>625.7488776155272</v>
       </c>
       <c r="D4" t="n">
-        <v>1221.537670552443</v>
+        <v>739.0680217405273</v>
       </c>
       <c r="E4" t="n">
-        <v>1339.366574763856</v>
+        <v>856.8969259519404</v>
       </c>
       <c r="F4" t="n">
-        <v>1463.727547355791</v>
+        <v>981.2578985438759</v>
       </c>
       <c r="G4" t="n">
-        <v>1463.727547355791</v>
+        <v>1134.664464430761</v>
       </c>
       <c r="H4" t="n">
-        <v>1463.727547355791</v>
+        <v>1304.181049590159</v>
       </c>
       <c r="I4" t="n">
-        <v>1463.727547355791</v>
+        <v>1525.313928526242</v>
       </c>
       <c r="J4" t="n">
-        <v>1463.727547355791</v>
+        <v>1525.313928526242</v>
       </c>
       <c r="K4" t="n">
-        <v>1546.422113931133</v>
+        <v>1546.422113931138</v>
       </c>
       <c r="L4" t="n">
-        <v>1546.422113931133</v>
+        <v>1522.636630943482</v>
       </c>
       <c r="M4" t="n">
-        <v>1424.572001403305</v>
+        <v>1400.786518415654</v>
       </c>
       <c r="N4" t="n">
-        <v>1251.657783957158</v>
+        <v>1227.872300969507</v>
       </c>
       <c r="O4" t="n">
-        <v>1008.783476806638</v>
+        <v>984.9979938189873</v>
       </c>
       <c r="P4" t="n">
-        <v>718.4320653639334</v>
+        <v>694.6465823762828</v>
       </c>
       <c r="Q4" t="n">
-        <v>389.3014932168646</v>
+        <v>365.5160102292141</v>
       </c>
       <c r="R4" t="n">
         <v>65.12</v>
@@ -4515,16 +4515,16 @@
         <v>499.7468717970915</v>
       </c>
       <c r="V4" t="n">
-        <v>698.5682646830375</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="W4" t="n">
-        <v>870.4591829427148</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="X4" t="n">
-        <v>870.4591829427148</v>
+        <v>499.7468717970915</v>
       </c>
       <c r="Y4" t="n">
-        <v>870.4591829427148</v>
+        <v>499.7468717970915</v>
       </c>
     </row>
     <row r="5">
@@ -4534,22 +4534,22 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1049.365529973416</v>
+        <v>1510.488528253487</v>
       </c>
       <c r="C5" t="n">
-        <v>999.3912085158463</v>
+        <v>1460.514206795918</v>
       </c>
       <c r="D5" t="n">
-        <v>988.9476168594324</v>
+        <v>1046.0302110991</v>
       </c>
       <c r="E5" t="n">
-        <v>984.5402536201711</v>
+        <v>637.5824438194345</v>
       </c>
       <c r="F5" t="n">
-        <v>632.6434249224528</v>
+        <v>228.6030208820488</v>
       </c>
       <c r="G5" t="n">
-        <v>628.8480993800122</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H5" t="n">
         <v>216.7171309926107</v>
@@ -4558,16 +4558,16 @@
         <v>65.12</v>
       </c>
       <c r="J5" t="n">
-        <v>448.0120508495619</v>
+        <v>65.1199999999717</v>
       </c>
       <c r="K5" t="n">
-        <v>431.6498286273396</v>
+        <v>115.3321502332765</v>
       </c>
       <c r="L5" t="n">
-        <v>415.2876064051172</v>
+        <v>98.96992801105415</v>
       </c>
       <c r="M5" t="n">
-        <v>920.1465133829101</v>
+        <v>603.8288349888471</v>
       </c>
       <c r="N5" t="n">
         <v>1213.137788947385</v>
@@ -4585,25 +4585,25 @@
         <v>3256</v>
       </c>
       <c r="S5" t="n">
-        <v>2756.153365856239</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T5" t="n">
-        <v>2163.551768150619</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U5" t="n">
-        <v>1911.813084768184</v>
+        <v>2372.936083048255</v>
       </c>
       <c r="V5" t="n">
-        <v>1679.640333084523</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W5" t="n">
-        <v>1438.859044214879</v>
+        <v>1899.982042494951</v>
       </c>
       <c r="X5" t="n">
-        <v>1244.634970012185</v>
+        <v>1705.757968292256</v>
       </c>
       <c r="Y5" t="n">
-        <v>1132.193118817431</v>
+        <v>1593.316117097502</v>
       </c>
     </row>
     <row r="6">
@@ -4613,16 +4613,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>931.509519579215</v>
+        <v>781.3195952961838</v>
       </c>
       <c r="C6" t="n">
-        <v>931.509519579215</v>
+        <v>416.5722089875784</v>
       </c>
       <c r="D6" t="n">
-        <v>754.3203429896864</v>
+        <v>65.12</v>
       </c>
       <c r="E6" t="n">
-        <v>408.1869114524009</v>
+        <v>65.12</v>
       </c>
       <c r="F6" t="n">
         <v>65.12</v>
@@ -4692,37 +4692,37 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>810.0297405151414</v>
+        <v>288.2866383453244</v>
       </c>
       <c r="C7" t="n">
-        <v>936.0317463335772</v>
+        <v>414.2886441637602</v>
       </c>
       <c r="D7" t="n">
-        <v>1049.350890458577</v>
+        <v>527.6077882887603</v>
       </c>
       <c r="E7" t="n">
-        <v>1167.17979466999</v>
+        <v>645.4366925001733</v>
       </c>
       <c r="F7" t="n">
-        <v>1291.540767261926</v>
+        <v>769.7976650921088</v>
       </c>
       <c r="G7" t="n">
-        <v>1444.947333148811</v>
+        <v>923.204230978994</v>
       </c>
       <c r="H7" t="n">
-        <v>1546.422113931141</v>
+        <v>1092.720816138392</v>
       </c>
       <c r="I7" t="n">
-        <v>1546.422113931141</v>
+        <v>1313.853695074475</v>
       </c>
       <c r="J7" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="K7" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="L7" t="n">
-        <v>1546.422113931141</v>
+        <v>1546.422113931142</v>
       </c>
       <c r="M7" t="n">
         <v>1430.29164756134</v>
@@ -4752,16 +4752,16 @@
         <v>65.12</v>
       </c>
       <c r="V7" t="n">
-        <v>263.941392885946</v>
+        <v>65.12</v>
       </c>
       <c r="W7" t="n">
-        <v>435.8323111456234</v>
+        <v>65.12</v>
       </c>
       <c r="X7" t="n">
-        <v>586.8631021698169</v>
+        <v>65.12</v>
       </c>
       <c r="Y7" t="n">
-        <v>698.2724028488492</v>
+        <v>176.5293006790322</v>
       </c>
     </row>
     <row r="8">
@@ -4771,25 +4771,25 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1358.891397260877</v>
+        <v>298.3673161322752</v>
       </c>
       <c r="C8" t="n">
-        <v>1308.917075803307</v>
+        <v>248.3929946747056</v>
       </c>
       <c r="D8" t="n">
-        <v>1298.473484146893</v>
+        <v>237.9494030182917</v>
       </c>
       <c r="E8" t="n">
-        <v>890.0257168672279</v>
+        <v>233.5420397790304</v>
       </c>
       <c r="F8" t="n">
-        <v>885.0866979702462</v>
+        <v>228.6030208820488</v>
       </c>
       <c r="G8" t="n">
-        <v>477.2509683874014</v>
+        <v>224.8076953396081</v>
       </c>
       <c r="H8" t="n">
-        <v>65.12</v>
+        <v>216.7171309926107</v>
       </c>
       <c r="I8" t="n">
         <v>65.12</v>
@@ -4798,19 +4798,19 @@
         <v>448.0120508495621</v>
       </c>
       <c r="K8" t="n">
-        <v>937.5543724554943</v>
+        <v>1155.766108953703</v>
       </c>
       <c r="L8" t="n">
-        <v>921.1921502332721</v>
+        <v>1743.414372455498</v>
       </c>
       <c r="M8" t="n">
-        <v>1426.051057211065</v>
+        <v>2248.273279433291</v>
       </c>
       <c r="N8" t="n">
-        <v>2035.360011169603</v>
+        <v>2857.58223339183</v>
       </c>
       <c r="O8" t="n">
-        <v>2841.220011169603</v>
+        <v>2841.220011169607</v>
       </c>
       <c r="P8" t="n">
         <v>2824.857788947385</v>
@@ -4819,28 +4819,28 @@
         <v>3256</v>
       </c>
       <c r="R8" t="n">
-        <v>3256</v>
+        <v>3002.587273910814</v>
       </c>
       <c r="S8" t="n">
-        <v>2756.153365856239</v>
+        <v>2813.235960095906</v>
       </c>
       <c r="T8" t="n">
-        <v>2473.077635438079</v>
+        <v>2624.67476643069</v>
       </c>
       <c r="U8" t="n">
-        <v>2221.338952055644</v>
+        <v>2372.936083048255</v>
       </c>
       <c r="V8" t="n">
-        <v>1989.166200371984</v>
+        <v>2140.763331364595</v>
       </c>
       <c r="W8" t="n">
-        <v>1748.38491150234</v>
+        <v>1495.941638454547</v>
       </c>
       <c r="X8" t="n">
-        <v>1554.160837299645</v>
+        <v>897.6771602114479</v>
       </c>
       <c r="Y8" t="n">
-        <v>1441.718986104891</v>
+        <v>381.1949049762899</v>
       </c>
     </row>
     <row r="9">
@@ -4850,10 +4850,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>139.0281492293901</v>
+        <v>124.0434662800893</v>
       </c>
       <c r="C9" t="n">
-        <v>65.12</v>
+        <v>124.0434662800893</v>
       </c>
       <c r="D9" t="n">
         <v>65.12</v>
@@ -4919,7 +4919,7 @@
         <v>527.4691155388109</v>
       </c>
       <c r="Y9" t="n">
-        <v>527.4691155388109</v>
+        <v>124.0434662800893</v>
       </c>
     </row>
     <row r="10">
@@ -4929,52 +4929,52 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>649.8117732085612</v>
+        <v>847.2278204562427</v>
       </c>
       <c r="C10" t="n">
-        <v>649.8117732085612</v>
+        <v>847.2278204562427</v>
       </c>
       <c r="D10" t="n">
-        <v>649.8117732085612</v>
+        <v>847.2278204562427</v>
       </c>
       <c r="E10" t="n">
-        <v>767.6406774199743</v>
+        <v>847.2278204562427</v>
       </c>
       <c r="F10" t="n">
-        <v>892.0016500119098</v>
+        <v>847.2278204562427</v>
       </c>
       <c r="G10" t="n">
-        <v>1045.408215898795</v>
+        <v>1000.634386343128</v>
       </c>
       <c r="H10" t="n">
-        <v>1214.924801058193</v>
+        <v>1170.150971502526</v>
       </c>
       <c r="I10" t="n">
-        <v>1436.057679994276</v>
+        <v>1391.283850438609</v>
       </c>
       <c r="J10" t="n">
-        <v>1436.057679994276</v>
+        <v>1436.057679994266</v>
       </c>
       <c r="K10" t="n">
-        <v>1546.422113931144</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="L10" t="n">
-        <v>1522.636630943488</v>
+        <v>1546.422113931135</v>
       </c>
       <c r="M10" t="n">
-        <v>1400.78651841566</v>
+        <v>1430.29164756134</v>
       </c>
       <c r="N10" t="n">
-        <v>1227.872300969514</v>
+        <v>1257.377430115193</v>
       </c>
       <c r="O10" t="n">
-        <v>984.9979938189937</v>
+        <v>1014.503122964673</v>
       </c>
       <c r="P10" t="n">
-        <v>694.6465823762892</v>
+        <v>724.1517115219688</v>
       </c>
       <c r="Q10" t="n">
-        <v>365.5160102292205</v>
+        <v>395.0211393749001</v>
       </c>
       <c r="R10" t="n">
         <v>65.12</v>
@@ -4986,19 +4986,19 @@
         <v>290.445934252978</v>
       </c>
       <c r="U10" t="n">
-        <v>477.9208549488839</v>
+        <v>536.9971268912645</v>
       </c>
       <c r="V10" t="n">
-        <v>477.9208549488839</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="W10" t="n">
-        <v>649.8117732085612</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="X10" t="n">
-        <v>649.8117732085612</v>
+        <v>735.8185197772104</v>
       </c>
       <c r="Y10" t="n">
-        <v>649.8117732085612</v>
+        <v>847.2278204562427</v>
       </c>
     </row>
     <row r="11">
@@ -5008,22 +5008,22 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>443.3049239128102</v>
+        <v>715.8788307838431</v>
       </c>
       <c r="C11" t="n">
-        <v>216.5629256875638</v>
+        <v>612.8599767862706</v>
       </c>
       <c r="D11" t="n">
-        <v>65.12</v>
+        <v>612.8599767862706</v>
       </c>
       <c r="E11" t="n">
-        <v>65.12</v>
+        <v>431.6849367793326</v>
       </c>
       <c r="F11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="G11" t="n">
-        <v>65.12</v>
+        <v>249.9782411146742</v>
       </c>
       <c r="H11" t="n">
         <v>65.12</v>
@@ -5038,13 +5038,13 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L11" t="n">
-        <v>1693.331756443634</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M11" t="n">
-        <v>2204.180585172569</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N11" t="n">
-        <v>2817.400904947332</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O11" t="n">
         <v>2817.400904947332</v>
@@ -5059,25 +5059,25 @@
         <v>3256</v>
       </c>
       <c r="S11" t="n">
-        <v>2983.426093128967</v>
+        <v>3256</v>
       </c>
       <c r="T11" t="n">
-        <v>2618.097222696074</v>
+        <v>2890.671129567107</v>
       </c>
       <c r="U11" t="n">
-        <v>2189.590862545962</v>
+        <v>2462.164769416995</v>
       </c>
       <c r="V11" t="n">
-        <v>1780.650434094625</v>
+        <v>2053.224340965658</v>
       </c>
       <c r="W11" t="n">
-        <v>1363.101468457304</v>
+        <v>1635.675375328337</v>
       </c>
       <c r="X11" t="n">
-        <v>992.1097174869324</v>
+        <v>1264.683624357965</v>
       </c>
       <c r="Y11" t="n">
-        <v>702.9001895245017</v>
+        <v>975.4740963955346</v>
       </c>
     </row>
     <row r="12">
@@ -5117,16 +5117,16 @@
         <v>831.5642142372474</v>
       </c>
       <c r="L12" t="n">
-        <v>1325.664675832448</v>
+        <v>1121.840378378698</v>
       </c>
       <c r="M12" t="n">
-        <v>1634.495217575307</v>
+        <v>1430.670920121557</v>
       </c>
       <c r="N12" t="n">
-        <v>1990.525502182875</v>
+        <v>1786.701204729125</v>
       </c>
       <c r="O12" t="n">
-        <v>2452.317953866594</v>
+        <v>2248.493656412844</v>
       </c>
       <c r="P12" t="n">
         <v>2583.773000882351</v>
@@ -5211,7 +5211,7 @@
         <v>409.3389893823512</v>
       </c>
       <c r="Q13" t="n">
-        <v>65.12</v>
+        <v>409.3389893823512</v>
       </c>
       <c r="R13" t="n">
         <v>65.12</v>
@@ -5254,13 +5254,13 @@
         <v>291.9779198897361</v>
       </c>
       <c r="E14" t="n">
-        <v>137.0655061454243</v>
+        <v>291.9779198897361</v>
       </c>
       <c r="F14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="G14" t="n">
-        <v>65.12</v>
+        <v>223.7156148520479</v>
       </c>
       <c r="H14" t="n">
         <v>65.12</v>
@@ -5275,13 +5275,13 @@
         <v>1166.135479385524</v>
       </c>
       <c r="L14" t="n">
-        <v>1693.331756443634</v>
+        <v>1166.135479385524</v>
       </c>
       <c r="M14" t="n">
-        <v>2204.180585172569</v>
+        <v>1676.984308114459</v>
       </c>
       <c r="N14" t="n">
-        <v>2817.400904947332</v>
+        <v>2290.204627889222</v>
       </c>
       <c r="O14" t="n">
         <v>2817.400904947332</v>
@@ -5348,19 +5348,19 @@
         <v>98.65487796756496</v>
       </c>
       <c r="J15" t="n">
-        <v>222.6113981428639</v>
+        <v>387.1477067497204</v>
       </c>
       <c r="K15" t="n">
-        <v>411.8042142372473</v>
+        <v>824.8305228441038</v>
       </c>
       <c r="L15" t="n">
-        <v>931.6446758324474</v>
+        <v>1096.180984439304</v>
       </c>
       <c r="M15" t="n">
-        <v>1266.215217575307</v>
+        <v>1430.751526182163</v>
       </c>
       <c r="N15" t="n">
-        <v>1399.495502182875</v>
+        <v>1564.031810789731</v>
       </c>
       <c r="O15" t="n">
         <v>1803.074262473451</v>
@@ -5439,16 +5439,16 @@
         <v>599.0397446017254</v>
       </c>
       <c r="N16" t="n">
-        <v>458.4993576555707</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="O16" t="n">
-        <v>65.12</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="P16" t="n">
-        <v>65.12</v>
+        <v>599.0397446017254</v>
       </c>
       <c r="Q16" t="n">
-        <v>65.12</v>
+        <v>545.5261898799506</v>
       </c>
       <c r="R16" t="n">
         <v>65.12</v>
@@ -5482,19 +5482,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>880.1035184729978</v>
+        <v>879.6685602764463</v>
       </c>
       <c r="C17" t="n">
-        <v>707.906974793206</v>
+        <v>707.4720165966545</v>
       </c>
       <c r="D17" t="n">
-        <v>575.2411609145698</v>
+        <v>574.8062027180183</v>
       </c>
       <c r="E17" t="n">
-        <v>448.6115754530863</v>
+        <v>448.1766172565348</v>
       </c>
       <c r="F17" t="n">
-        <v>321.4503343338824</v>
+        <v>321.0153761373309</v>
       </c>
       <c r="G17" t="n">
         <v>195.4327865692196</v>
@@ -5506,22 +5506,22 @@
         <v>65.12</v>
       </c>
       <c r="J17" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K17" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L17" t="n">
-        <v>1262.289113037656</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M17" t="n">
-        <v>1773.137941766591</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N17" t="n">
-        <v>2011.540904947332</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O17" t="n">
-        <v>2011.540904947332</v>
+        <v>2817.400904947332</v>
       </c>
       <c r="P17" t="n">
         <v>2817.400904947332</v>
@@ -5533,25 +5533,25 @@
         <v>3256</v>
       </c>
       <c r="S17" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T17" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U17" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V17" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W17" t="n">
-        <v>1636.263699381128</v>
+        <v>1635.828741184576</v>
       </c>
       <c r="X17" t="n">
-        <v>1319.817402956211</v>
+        <v>1319.382444759659</v>
       </c>
       <c r="Y17" t="n">
-        <v>1085.153329539235</v>
+        <v>1084.718371342683</v>
       </c>
     </row>
     <row r="18">
@@ -5582,28 +5582,28 @@
         <v>65.12</v>
       </c>
       <c r="I18" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J18" t="n">
-        <v>250.3313981428639</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K18" t="n">
-        <v>715.7342142372473</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L18" t="n">
-        <v>987.0846758324474</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M18" t="n">
-        <v>1073.165217575307</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N18" t="n">
-        <v>1465.420914107732</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O18" t="n">
-        <v>1704.463365791451</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P18" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q18" t="n">
         <v>1816.992710260958</v>
@@ -5682,10 +5682,10 @@
         <v>859.3027230120967</v>
       </c>
       <c r="P19" t="n">
-        <v>859.3027230120967</v>
+        <v>516.472794369291</v>
       </c>
       <c r="Q19" t="n">
-        <v>517.2433615971223</v>
+        <v>65.12</v>
       </c>
       <c r="R19" t="n">
         <v>65.12</v>
@@ -5743,19 +5743,19 @@
         <v>65.12</v>
       </c>
       <c r="J20" t="n">
-        <v>456.4291130376557</v>
+        <v>65.12</v>
       </c>
       <c r="K20" t="n">
-        <v>456.4291130376557</v>
+        <v>774.8263663478684</v>
       </c>
       <c r="L20" t="n">
-        <v>887.4717564436343</v>
+        <v>1580.686366347868</v>
       </c>
       <c r="M20" t="n">
-        <v>1398.320585172569</v>
+        <v>2091.535195076804</v>
       </c>
       <c r="N20" t="n">
-        <v>2011.540904947332</v>
+        <v>2704.755514851567</v>
       </c>
       <c r="O20" t="n">
         <v>2817.400904947332</v>
@@ -5770,16 +5770,16 @@
         <v>3256</v>
       </c>
       <c r="S20" t="n">
-        <v>3038.406505870973</v>
+        <v>3037.971547674421</v>
       </c>
       <c r="T20" t="n">
-        <v>2727.623089983534</v>
+        <v>2727.188131786983</v>
       </c>
       <c r="U20" t="n">
-        <v>2353.662184378877</v>
+        <v>2353.227226182325</v>
       </c>
       <c r="V20" t="n">
-        <v>1999.267210472994</v>
+        <v>1998.832252276443</v>
       </c>
       <c r="W20" t="n">
         <v>1636.263699381128</v>
@@ -5819,25 +5819,25 @@
         <v>65.12</v>
       </c>
       <c r="I21" t="n">
-        <v>126.374877967565</v>
+        <v>65.12</v>
       </c>
       <c r="J21" t="n">
-        <v>250.3313981428639</v>
+        <v>189.076520175299</v>
       </c>
       <c r="K21" t="n">
-        <v>439.5242142372473</v>
+        <v>378.2693362696824</v>
       </c>
       <c r="L21" t="n">
-        <v>710.8746758324473</v>
+        <v>649.6197978648825</v>
       </c>
       <c r="M21" t="n">
-        <v>796.9552175753066</v>
+        <v>735.7003396077417</v>
       </c>
       <c r="N21" t="n">
-        <v>930.2355021828749</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O21" t="n">
-        <v>1445.487953866594</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P21" t="n">
         <v>1712.131182700533</v>
@@ -5916,13 +5916,13 @@
         <v>859.3027230120967</v>
       </c>
       <c r="O22" t="n">
-        <v>517.2433615971223</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="P22" t="n">
-        <v>517.2433615971223</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="Q22" t="n">
-        <v>517.2433615971223</v>
+        <v>407.9499286428058</v>
       </c>
       <c r="R22" t="n">
         <v>65.12</v>
@@ -6007,16 +6007,16 @@
         <v>3256</v>
       </c>
       <c r="S23" t="n">
-        <v>3037.971547674421</v>
+        <v>3038.406505870973</v>
       </c>
       <c r="T23" t="n">
-        <v>2727.188131786983</v>
+        <v>2727.623089983534</v>
       </c>
       <c r="U23" t="n">
-        <v>2353.227226182325</v>
+        <v>2353.662184378877</v>
       </c>
       <c r="V23" t="n">
-        <v>1998.832252276443</v>
+        <v>1999.267210472994</v>
       </c>
       <c r="W23" t="n">
         <v>1636.263699381128</v>
@@ -6071,13 +6071,13 @@
         <v>735.7003396077417</v>
       </c>
       <c r="N24" t="n">
-        <v>1145.19062421531</v>
+        <v>868.9806242153101</v>
       </c>
       <c r="O24" t="n">
-        <v>1660.443075899029</v>
+        <v>1323.391838231026</v>
       </c>
       <c r="P24" t="n">
-        <v>1816.992710260958</v>
+        <v>1712.131182700533</v>
       </c>
       <c r="Q24" t="n">
         <v>1816.992710260958</v>
@@ -6114,55 +6114,55 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>414.3442160506673</v>
+        <v>422.5399739669084</v>
       </c>
       <c r="C25" t="n">
-        <v>420.5562218691031</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="D25" t="n">
-        <v>413.953981408946</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="E25" t="n">
-        <v>411.9530674322223</v>
+        <v>428.7519797853442</v>
       </c>
       <c r="F25" t="n">
-        <v>416.5240400241578</v>
+        <v>433.3229523772797</v>
       </c>
       <c r="G25" t="n">
-        <v>450.1406059110431</v>
+        <v>466.939518264165</v>
       </c>
       <c r="H25" t="n">
-        <v>499.8671910704406</v>
+        <v>516.6661034235625</v>
       </c>
       <c r="I25" t="n">
-        <v>601.2100700065236</v>
+        <v>618.0089823596454</v>
       </c>
       <c r="J25" t="n">
-        <v>842.5038106589749</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="K25" t="n">
-        <v>832.886867425497</v>
+        <v>859.3027230120967</v>
       </c>
       <c r="L25" t="n">
-        <v>686.8791622156191</v>
+        <v>713.2950178022188</v>
       </c>
       <c r="M25" t="n">
-        <v>477.6936336649268</v>
+        <v>469.2226830521684</v>
       </c>
       <c r="N25" t="n">
-        <v>477.6936336649268</v>
+        <v>174.0862433837998</v>
       </c>
       <c r="O25" t="n">
-        <v>477.6936336649268</v>
+        <v>174.0862433837998</v>
       </c>
       <c r="P25" t="n">
-        <v>65.12</v>
+        <v>174.0862433837998</v>
       </c>
       <c r="Q25" t="n">
-        <v>65.12</v>
+        <v>174.0862433837998</v>
       </c>
       <c r="R25" t="n">
-        <v>65.12</v>
+        <v>149.3356360634903</v>
       </c>
       <c r="S25" t="n">
         <v>65.12</v>
@@ -6193,22 +6193,22 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1022.921205738787</v>
+        <v>542.3744530587821</v>
       </c>
       <c r="C26" t="n">
-        <v>796.1792075135407</v>
+        <v>315.6324548335357</v>
       </c>
       <c r="D26" t="n">
-        <v>608.9679390894501</v>
+        <v>315.6324548335357</v>
       </c>
       <c r="E26" t="n">
-        <v>608.9679390894501</v>
+        <v>243.5466956646584</v>
       </c>
       <c r="F26" t="n">
-        <v>427.2612434247916</v>
+        <v>61.84</v>
       </c>
       <c r="G26" t="n">
-        <v>246.6982411146742</v>
+        <v>61.84</v>
       </c>
       <c r="H26" t="n">
         <v>61.84</v>
@@ -6220,22 +6220,22 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K26" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L26" t="n">
-        <v>453.1491130376558</v>
+        <v>1928.125479385524</v>
       </c>
       <c r="M26" t="n">
-        <v>963.9979417665908</v>
+        <v>2438.974308114459</v>
       </c>
       <c r="N26" t="n">
-        <v>1122.86090494728</v>
+        <v>3052.194627889222</v>
       </c>
       <c r="O26" t="n">
-        <v>1888.130904947306</v>
+        <v>3092</v>
       </c>
       <c r="P26" t="n">
-        <v>2653.400904947332</v>
+        <v>3092</v>
       </c>
       <c r="Q26" t="n">
         <v>3092</v>
@@ -6250,19 +6250,19 @@
         <v>2427.957223879615</v>
       </c>
       <c r="U26" t="n">
-        <v>2360.266715920602</v>
+        <v>1999.450863729503</v>
       </c>
       <c r="V26" t="n">
-        <v>2360.266715920602</v>
+        <v>1590.510435278166</v>
       </c>
       <c r="W26" t="n">
-        <v>1942.717750283281</v>
+        <v>1172.961469640845</v>
       </c>
       <c r="X26" t="n">
-        <v>1571.725999312909</v>
+        <v>801.9697186704736</v>
       </c>
       <c r="Y26" t="n">
-        <v>1282.516471350479</v>
+        <v>801.9697186704736</v>
       </c>
     </row>
     <row r="27">
@@ -6293,16 +6293,16 @@
         <v>61.84</v>
       </c>
       <c r="I27" t="n">
-        <v>61.84</v>
+        <v>69.63487796756496</v>
       </c>
       <c r="J27" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K27" t="n">
-        <v>624.4599167834981</v>
+        <v>828.2842142372474</v>
       </c>
       <c r="L27" t="n">
-        <v>1118.560378378698</v>
+        <v>1322.384675832448</v>
       </c>
       <c r="M27" t="n">
         <v>1427.390920121557</v>
@@ -6351,55 +6351,55 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="C28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="D28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="E28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="F28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="G28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="H28" t="n">
-        <v>171.7290463985742</v>
+        <v>170.342369793817</v>
       </c>
       <c r="I28" t="n">
-        <v>219.6119253346571</v>
+        <v>218.2252487298999</v>
       </c>
       <c r="J28" t="n">
-        <v>407.4456659871084</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="K28" t="n">
-        <v>407.4456659871084</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="L28" t="n">
-        <v>407.4456659871084</v>
+        <v>406.0589893823512</v>
       </c>
       <c r="M28" t="n">
-        <v>407.4456659871084</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="N28" t="n">
-        <v>407.4456659871084</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="O28" t="n">
-        <v>407.4456659871084</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="P28" t="n">
-        <v>407.4456659871084</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="Q28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="R28" t="n">
-        <v>61.84</v>
+        <v>200.6010906089449</v>
       </c>
       <c r="S28" t="n">
         <v>61.84</v>
@@ -6414,13 +6414,13 @@
         <v>175.5382646830375</v>
       </c>
       <c r="W28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="X28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
       <c r="Y28" t="n">
-        <v>175.5382646830375</v>
+        <v>174.1515880782802</v>
       </c>
     </row>
     <row r="29">
@@ -6430,22 +6430,22 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>475.7932666493371</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="C29" t="n">
-        <v>249.0512684240907</v>
+        <v>253.1649250963515</v>
       </c>
       <c r="D29" t="n">
-        <v>61.84</v>
+        <v>65.95365667226079</v>
       </c>
       <c r="E29" t="n">
-        <v>61.84</v>
+        <v>65.95365667226079</v>
       </c>
       <c r="F29" t="n">
-        <v>61.84</v>
+        <v>65.95365667226079</v>
       </c>
       <c r="G29" t="n">
-        <v>61.84</v>
+        <v>65.95365667226079</v>
       </c>
       <c r="H29" t="n">
         <v>61.84</v>
@@ -6457,10 +6457,10 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K29" t="n">
-        <v>453.1491130376558</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="L29" t="n">
-        <v>764.0617564436008</v>
+        <v>1162.855479385524</v>
       </c>
       <c r="M29" t="n">
         <v>1274.910585172536</v>
@@ -6533,7 +6533,7 @@
         <v>69.63487796756496</v>
       </c>
       <c r="J30" t="n">
-        <v>212.5171006891147</v>
+        <v>416.3413981428639</v>
       </c>
       <c r="K30" t="n">
         <v>624.4599167834981</v>
@@ -6624,10 +6624,10 @@
         <v>406.0589893823512</v>
       </c>
       <c r="N31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="O31" t="n">
-        <v>406.0589893823512</v>
+        <v>61.84</v>
       </c>
       <c r="P31" t="n">
         <v>61.84</v>
@@ -6694,16 +6694,16 @@
         <v>445.5561922637026</v>
       </c>
       <c r="K32" t="n">
-        <v>430.940588376518</v>
+        <v>430.0181114556216</v>
       </c>
       <c r="L32" t="n">
-        <v>415.4025075684371</v>
+        <v>415.4025075684356</v>
       </c>
       <c r="M32" t="n">
-        <v>921.0855559603708</v>
+        <v>921.0855559603693</v>
       </c>
       <c r="N32" t="n">
-        <v>1129.493647533164</v>
+        <v>1531.218651333048</v>
       </c>
       <c r="O32" t="n">
         <v>1894.763647533204</v>
@@ -6770,25 +6770,25 @@
         <v>134.974877967565</v>
       </c>
       <c r="J33" t="n">
-        <v>258.9313981428639</v>
+        <v>483.6771006891146</v>
       </c>
       <c r="K33" t="n">
-        <v>736.2142142372473</v>
+        <v>672.869916783498</v>
       </c>
       <c r="L33" t="n">
-        <v>1007.564675832447</v>
+        <v>944.220378378698</v>
       </c>
       <c r="M33" t="n">
-        <v>1093.645217575307</v>
+        <v>1030.300920121557</v>
       </c>
       <c r="N33" t="n">
-        <v>1226.925502182875</v>
+        <v>1163.581204729126</v>
       </c>
       <c r="O33" t="n">
-        <v>1465.967953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P33" t="n">
-        <v>1578.4972983361</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q33" t="n">
         <v>1631.894528442776</v>
@@ -6864,10 +6864,10 @@
         <v>1011.831843630703</v>
       </c>
       <c r="O34" t="n">
-        <v>1011.831843630703</v>
+        <v>658.8565263791725</v>
       </c>
       <c r="P34" t="n">
-        <v>611.3794220869881</v>
+        <v>658.8565263791725</v>
       </c>
       <c r="Q34" t="n">
         <v>573.9365734181883</v>
@@ -6904,22 +6904,22 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C35" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D35" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E35" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F35" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G35" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H35" t="n">
         <v>61.84</v>
@@ -6931,49 +6931,49 @@
         <v>445.5561922637025</v>
       </c>
       <c r="K35" t="n">
-        <v>430.9405883765174</v>
+        <v>1155.056868702881</v>
       </c>
       <c r="L35" t="n">
-        <v>415.4025075684365</v>
+        <v>1139.5187878948</v>
       </c>
       <c r="M35" t="n">
-        <v>921.0855559603701</v>
+        <v>1645.201836286734</v>
       </c>
       <c r="N35" t="n">
-        <v>1531.218651333049</v>
+        <v>2255.334931659412</v>
       </c>
       <c r="O35" t="n">
-        <v>2296.488651333097</v>
+        <v>2239.79685085133</v>
       </c>
       <c r="P35" t="n">
-        <v>3061.758651333145</v>
+        <v>2660.033647533245</v>
       </c>
       <c r="Q35" t="n">
         <v>3092</v>
       </c>
       <c r="R35" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S35" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T35" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U35" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V35" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W35" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X35" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y35" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="36">
@@ -7022,10 +7022,10 @@
         <v>938.8355021828751</v>
       </c>
       <c r="O36" t="n">
-        <v>1177.877953866594</v>
+        <v>1402.623656412844</v>
       </c>
       <c r="P36" t="n">
-        <v>1578.497298336101</v>
+        <v>1515.153000882351</v>
       </c>
       <c r="Q36" t="n">
         <v>1631.894528442776</v>
@@ -7092,25 +7092,25 @@
         <v>1011.831843630703</v>
       </c>
       <c r="L37" t="n">
-        <v>1011.831843630703</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M37" t="n">
-        <v>1011.831843630703</v>
+        <v>645.9942279131988</v>
       </c>
       <c r="N37" t="n">
-        <v>1011.831843630703</v>
+        <v>362.9790003660423</v>
       </c>
       <c r="O37" t="n">
-        <v>1011.831843630703</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="P37" t="n">
-        <v>611.3794220869881</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="Q37" t="n">
-        <v>172.1478398389093</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R37" t="n">
-        <v>61.84</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="S37" t="n">
         <v>61.84</v>
@@ -7141,22 +7141,22 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>812.6382572461436</v>
+        <v>804.0962457457251</v>
       </c>
       <c r="C38" t="n">
-        <v>652.5629256875638</v>
+        <v>644.0209141871454</v>
       </c>
       <c r="D38" t="n">
-        <v>532.0183239301398</v>
+        <v>523.4763124297214</v>
       </c>
       <c r="E38" t="n">
-        <v>417.5099505898684</v>
+        <v>408.96793908945</v>
       </c>
       <c r="F38" t="n">
-        <v>302.4699215918766</v>
+        <v>293.9279100914582</v>
       </c>
       <c r="G38" t="n">
-        <v>188.5735859484259</v>
+        <v>180.0315744480075</v>
       </c>
       <c r="H38" t="n">
         <v>61.84</v>
@@ -7168,19 +7168,19 @@
         <v>445.5561922637023</v>
       </c>
       <c r="K38" t="n">
-        <v>430.9405883765124</v>
+        <v>1154.134391781985</v>
       </c>
       <c r="L38" t="n">
-        <v>415.4025075684315</v>
+        <v>1138.596310973903</v>
       </c>
       <c r="M38" t="n">
-        <v>921.0855559603649</v>
+        <v>1644.279359365837</v>
       </c>
       <c r="N38" t="n">
-        <v>1531.218651333043</v>
+        <v>2254.412454738515</v>
       </c>
       <c r="O38" t="n">
-        <v>1894.763647533191</v>
+        <v>2193.441226685607</v>
       </c>
       <c r="P38" t="n">
         <v>2660.033647533246</v>
@@ -7189,28 +7189,28 @@
         <v>3092</v>
       </c>
       <c r="R38" t="n">
-        <v>3092</v>
+        <v>3083.457988499581</v>
       </c>
       <c r="S38" t="n">
-        <v>2886.092759795633</v>
+        <v>2877.550748295214</v>
       </c>
       <c r="T38" t="n">
-        <v>2587.430556029407</v>
+        <v>2578.888544528988</v>
       </c>
       <c r="U38" t="n">
-        <v>2225.590862545962</v>
+        <v>2217.048851045543</v>
       </c>
       <c r="V38" t="n">
-        <v>1883.317100761291</v>
+        <v>1874.775089260873</v>
       </c>
       <c r="W38" t="n">
-        <v>1532.434801790637</v>
+        <v>1523.892790290219</v>
       </c>
       <c r="X38" t="n">
-        <v>1228.109717486932</v>
+        <v>1219.567705986514</v>
       </c>
       <c r="Y38" t="n">
-        <v>1005.566856191168</v>
+        <v>997.0248446907499</v>
       </c>
     </row>
     <row r="39">
@@ -7244,16 +7244,16 @@
         <v>134.974877967565</v>
       </c>
       <c r="J39" t="n">
-        <v>483.6771006891146</v>
+        <v>258.9313981428639</v>
       </c>
       <c r="K39" t="n">
-        <v>672.869916783498</v>
+        <v>448.1242142372473</v>
       </c>
       <c r="L39" t="n">
-        <v>944.220378378698</v>
+        <v>719.4746758324475</v>
       </c>
       <c r="M39" t="n">
-        <v>1030.300920121557</v>
+        <v>805.5552175753068</v>
       </c>
       <c r="N39" t="n">
         <v>1163.581204729126</v>
@@ -7299,52 +7299,52 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>486.0066123122601</v>
+        <v>486.0066123122328</v>
       </c>
       <c r="C40" t="n">
-        <v>504.0986181306959</v>
+        <v>504.0986181306686</v>
       </c>
       <c r="D40" t="n">
-        <v>509.507762255696</v>
+        <v>509.5077622556687</v>
       </c>
       <c r="E40" t="n">
-        <v>519.426666467109</v>
+        <v>519.4266664670818</v>
       </c>
       <c r="F40" t="n">
-        <v>535.8776390590446</v>
+        <v>535.8776390590173</v>
       </c>
       <c r="G40" t="n">
-        <v>581.3742049459298</v>
+        <v>581.3742049459025</v>
       </c>
       <c r="H40" t="n">
-        <v>642.9807901053274</v>
+        <v>642.9807901053001</v>
       </c>
       <c r="I40" t="n">
-        <v>756.2036690414103</v>
+        <v>756.203669041383</v>
       </c>
       <c r="J40" t="n">
-        <v>1009.377409693862</v>
+        <v>1009.377409693834</v>
       </c>
       <c r="K40" t="n">
-        <v>1011.83184363073</v>
+        <v>1011.831843630703</v>
       </c>
       <c r="L40" t="n">
-        <v>877.9453505420643</v>
+        <v>877.945350542037</v>
       </c>
       <c r="M40" t="n">
-        <v>645.994227913226</v>
+        <v>877.945350542037</v>
       </c>
       <c r="N40" t="n">
-        <v>573.9365734181883</v>
+        <v>877.945350542037</v>
       </c>
       <c r="O40" t="n">
-        <v>573.9365734181883</v>
+        <v>877.945350542037</v>
       </c>
       <c r="P40" t="n">
-        <v>573.9365734181883</v>
+        <v>573.1660061903571</v>
       </c>
       <c r="Q40" t="n">
-        <v>573.9365734181883</v>
+        <v>133.9344239422782</v>
       </c>
       <c r="R40" t="n">
         <v>133.9344239422782</v>
@@ -7365,10 +7365,10 @@
         <v>435.5391829427149</v>
       </c>
       <c r="X40" t="n">
-        <v>478.6599739669358</v>
+        <v>478.6599739669085</v>
       </c>
       <c r="Y40" t="n">
-        <v>482.159274645968</v>
+        <v>482.1592746459407</v>
       </c>
     </row>
     <row r="41">
@@ -7378,22 +7378,22 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>1084.139304041668</v>
+        <v>415.7904937383461</v>
       </c>
       <c r="C41" t="n">
-        <v>845.2760936952099</v>
+        <v>176.9272833918876</v>
       </c>
       <c r="D41" t="n">
-        <v>645.943613149907</v>
+        <v>61.84</v>
       </c>
       <c r="E41" t="n">
-        <v>452.6473610217569</v>
+        <v>61.84</v>
       </c>
       <c r="F41" t="n">
-        <v>258.8194532358863</v>
+        <v>61.84</v>
       </c>
       <c r="G41" t="n">
-        <v>258.8194532358863</v>
+        <v>61.84</v>
       </c>
       <c r="H41" t="n">
         <v>61.84</v>
@@ -7405,19 +7405,19 @@
         <v>453.1491130376558</v>
       </c>
       <c r="K41" t="n">
-        <v>453.1491130376558</v>
+        <v>764.0617564435721</v>
       </c>
       <c r="L41" t="n">
-        <v>453.1491130376558</v>
+        <v>764.0617564435721</v>
       </c>
       <c r="M41" t="n">
-        <v>963.9979417665908</v>
+        <v>1274.910585172507</v>
       </c>
       <c r="N41" t="n">
-        <v>1122.860904947208</v>
+        <v>1888.13090494727</v>
       </c>
       <c r="O41" t="n">
-        <v>1888.13090494727</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P41" t="n">
         <v>2653.400904947332</v>
@@ -7426,28 +7426,28 @@
         <v>3092</v>
       </c>
       <c r="R41" t="n">
-        <v>3092</v>
+        <v>3053.738789062329</v>
       </c>
       <c r="S41" t="n">
-        <v>2807.304881007754</v>
+        <v>2769.043670070084</v>
       </c>
       <c r="T41" t="n">
-        <v>2480.927057221122</v>
+        <v>2391.593587515979</v>
       </c>
       <c r="U41" t="n">
-        <v>2040.299484949798</v>
+        <v>1950.966015244655</v>
       </c>
       <c r="V41" t="n">
-        <v>2040.299484949798</v>
+        <v>1529.904374672105</v>
       </c>
       <c r="W41" t="n">
-        <v>2040.299484949798</v>
+        <v>1100.234196913573</v>
       </c>
       <c r="X41" t="n">
-        <v>1657.186521858215</v>
+        <v>717.1212338219889</v>
       </c>
       <c r="Y41" t="n">
-        <v>1355.855781774572</v>
+        <v>415.7904937383461</v>
       </c>
     </row>
     <row r="42">
@@ -7496,28 +7496,28 @@
         <v>1920.05062421531</v>
       </c>
       <c r="O42" t="n">
-        <v>2369.963075899029</v>
+        <v>2316.104912118934</v>
       </c>
       <c r="P42" t="n">
-        <v>2556.7702160152</v>
+        <v>2639.504256588441</v>
       </c>
       <c r="Q42" t="n">
-        <v>2596.291743575625</v>
+        <v>2679.025784148866</v>
       </c>
       <c r="R42" t="n">
-        <v>2258.641443280292</v>
+        <v>2341.375483853533</v>
       </c>
       <c r="S42" t="n">
-        <v>2002.516190790786</v>
+        <v>2085.250231364027</v>
       </c>
       <c r="T42" t="n">
-        <v>1808.215417843802</v>
+        <v>1890.949458417043</v>
       </c>
       <c r="U42" t="n">
-        <v>1619.114044348664</v>
+        <v>1701.848084921905</v>
       </c>
       <c r="V42" t="n">
-        <v>1415.567915872381</v>
+        <v>1498.301956445622</v>
       </c>
       <c r="W42" t="n">
         <v>1415.567915872381</v>
@@ -7557,31 +7557,31 @@
         <v>61.84</v>
       </c>
       <c r="I43" t="n">
-        <v>97.84287893608291</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="J43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="K43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="L43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="M43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="N43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="O43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="P43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="Q43" t="n">
-        <v>237.4417908110377</v>
+        <v>91.27831913164476</v>
       </c>
       <c r="R43" t="n">
         <v>91.27831913164476</v>
@@ -7615,7 +7615,7 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>61.84</v>
+        <v>326.9658366090848</v>
       </c>
       <c r="C44" t="n">
         <v>61.84</v>
@@ -7642,19 +7642,19 @@
         <v>61.84</v>
       </c>
       <c r="K44" t="n">
-        <v>61.84</v>
+        <v>771.5463663478683</v>
       </c>
       <c r="L44" t="n">
-        <v>764.0617564435576</v>
+        <v>1529.331756443634</v>
       </c>
       <c r="M44" t="n">
-        <v>1274.910585172493</v>
+        <v>2040.180585172569</v>
       </c>
       <c r="N44" t="n">
-        <v>1888.130904947256</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="O44" t="n">
-        <v>1888.130904947256</v>
+        <v>2653.400904947332</v>
       </c>
       <c r="P44" t="n">
         <v>2653.400904947332</v>
@@ -7666,25 +7666,25 @@
         <v>3027.476162799703</v>
       </c>
       <c r="S44" t="n">
-        <v>2716.518417544831</v>
+        <v>3027.476162799703</v>
       </c>
       <c r="T44" t="n">
-        <v>2312.8057087281</v>
+        <v>2623.763453982971</v>
       </c>
       <c r="U44" t="n">
-        <v>1845.91551019415</v>
+        <v>2156.873255449021</v>
       </c>
       <c r="V44" t="n">
-        <v>1398.591243358974</v>
+        <v>1709.548988613845</v>
       </c>
       <c r="W44" t="n">
-        <v>942.6584393378148</v>
+        <v>1253.616184592686</v>
       </c>
       <c r="X44" t="n">
-        <v>533.2828499836049</v>
+        <v>952.5383069508837</v>
       </c>
       <c r="Y44" t="n">
-        <v>205.6894836373359</v>
+        <v>624.9449406046147</v>
       </c>
     </row>
     <row r="45">
@@ -7694,25 +7694,25 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>171.5851425821576</v>
+        <v>742.1150755498586</v>
       </c>
       <c r="C45" t="n">
-        <v>61.84</v>
+        <v>566.2565781301421</v>
       </c>
       <c r="D45" t="n">
-        <v>61.84</v>
+        <v>403.6932580314526</v>
       </c>
       <c r="E45" t="n">
-        <v>61.84</v>
+        <v>246.448715383056</v>
       </c>
       <c r="F45" t="n">
-        <v>61.84</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="G45" t="n">
-        <v>61.84</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="H45" t="n">
-        <v>61.84</v>
+        <v>92.27069281954398</v>
       </c>
       <c r="I45" t="n">
         <v>61.84</v>
@@ -7721,49 +7721,49 @@
         <v>370.9265201752989</v>
       </c>
       <c r="K45" t="n">
-        <v>599.0628755631702</v>
+        <v>745.2493362696823</v>
       </c>
       <c r="L45" t="n">
-        <v>1055.54333715837</v>
+        <v>1201.729797864882</v>
       </c>
       <c r="M45" t="n">
-        <v>1326.75387890123</v>
+        <v>1472.940339607742</v>
       </c>
       <c r="N45" t="n">
-        <v>1645.164163508798</v>
+        <v>1648.924168871373</v>
       </c>
       <c r="O45" t="n">
-        <v>2069.336615192517</v>
+        <v>2073.096620555092</v>
       </c>
       <c r="P45" t="n">
-        <v>2366.995959662024</v>
+        <v>2370.755965024599</v>
       </c>
       <c r="Q45" t="n">
-        <v>2380.777487222449</v>
+        <v>2384.537492585024</v>
       </c>
       <c r="R45" t="n">
-        <v>2016.86456066449</v>
+        <v>2057.154955375181</v>
       </c>
       <c r="S45" t="n">
-        <v>1734.476681912357</v>
+        <v>2057.154955375181</v>
       </c>
       <c r="T45" t="n">
-        <v>1513.913282702747</v>
+        <v>1836.591556165571</v>
       </c>
       <c r="U45" t="n">
-        <v>1298.549282944983</v>
+        <v>1621.227556407807</v>
       </c>
       <c r="V45" t="n">
-        <v>1068.740528206074</v>
+        <v>1391.418801668897</v>
       </c>
       <c r="W45" t="n">
-        <v>820.8888687011965</v>
+        <v>1391.418801668897</v>
       </c>
       <c r="X45" t="n">
-        <v>585.6739803725222</v>
+        <v>1156.203913340223</v>
       </c>
       <c r="Y45" t="n">
-        <v>371.1372200026896</v>
+        <v>941.6671529703906</v>
       </c>
     </row>
     <row r="46">
@@ -7773,22 +7773,22 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="C46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="D46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="E46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="F46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="G46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="H46" t="n">
         <v>61.84</v>
@@ -7797,52 +7797,52 @@
         <v>61.84</v>
       </c>
       <c r="J46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="K46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="L46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="M46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="N46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="O46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="P46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="Q46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="R46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="S46" t="n">
-        <v>143.8035716568973</v>
+        <v>137.1608955163471</v>
       </c>
       <c r="T46" t="n">
-        <v>143.8035716568973</v>
+        <v>113.9037576312383</v>
       </c>
       <c r="U46" t="n">
-        <v>143.8035716568973</v>
+        <v>113.9037576312383</v>
       </c>
       <c r="V46" t="n">
-        <v>143.8035716568973</v>
+        <v>101.6105149885956</v>
       </c>
       <c r="W46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="X46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
       <c r="Y46" t="n">
-        <v>104.0330566683016</v>
+        <v>61.84</v>
       </c>
     </row>
   </sheetData>
@@ -7964,22 +7964,22 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J2" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624509022</v>
       </c>
       <c r="K2" t="n">
         <v>716.8751175230994</v>
       </c>
       <c r="L2" t="n">
-        <v>597.9703808667776</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>1060.271045550332</v>
+        <v>544.2621276423173</v>
       </c>
       <c r="N2" t="n">
-        <v>1096.663422488788</v>
+        <v>961.7058516046468</v>
       </c>
       <c r="O2" t="n">
-        <v>70.24786957409242</v>
+        <v>884.2478695740924</v>
       </c>
       <c r="P2" t="n">
         <v>0.2870600406814674</v>
@@ -8201,10 +8201,10 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J5" t="n">
-        <v>430.3047365861567</v>
+        <v>51.24160624506226</v>
       </c>
       <c r="K5" t="n">
-        <v>0</v>
+        <v>65.90862873097186</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -8213,7 +8213,7 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N5" t="n">
-        <v>783.5089208786655</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O5" t="n">
         <v>884.2478695740924</v>
@@ -8441,10 +8441,10 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K8" t="n">
-        <v>500.8454983898731</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>597.9703808667776</v>
       </c>
       <c r="M8" t="n">
         <v>1060.271045550332</v>
@@ -8453,10 +8453,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O8" t="n">
-        <v>884.2478695740924</v>
+        <v>70.24786957409242</v>
       </c>
       <c r="P8" t="n">
-        <v>0.2870600406860149</v>
+        <v>0.2870600406814674</v>
       </c>
       <c r="Q8" t="n">
         <v>615.8520732695737</v>
@@ -8681,7 +8681,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L11" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>1060.271045550332</v>
@@ -8690,7 +8690,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O11" t="n">
-        <v>70.24786957409245</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P11" t="n">
         <v>0.2870600406814136</v>
@@ -8918,7 +8918,7 @@
         <v>716.8751175230994</v>
       </c>
       <c r="L14" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>1060.271045550332</v>
@@ -8927,7 +8927,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O14" t="n">
-        <v>70.24786957409245</v>
+        <v>602.7693615519817</v>
       </c>
       <c r="P14" t="n">
         <v>0.2870600406814136</v>
@@ -9149,25 +9149,25 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J17" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N17" t="n">
-        <v>718.0600319897762</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O17" t="n">
-        <v>70.24786957409245</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P17" t="n">
-        <v>814.2870600406815</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q17" t="n">
         <v>615.8520732695737</v>
@@ -9386,13 +9386,13 @@
         <v>120.6470157237802</v>
       </c>
       <c r="J20" t="n">
-        <v>430.3047365861567</v>
+        <v>35.04300624509033</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>435.3966095009885</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>1060.271045550332</v>
@@ -9401,7 +9401,7 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O20" t="n">
-        <v>884.2478695740924</v>
+        <v>184.0310918930479</v>
       </c>
       <c r="P20" t="n">
         <v>0.2870600406814136</v>
@@ -9863,25 +9863,25 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M26" t="n">
         <v>1060.271045550332</v>
       </c>
       <c r="N26" t="n">
-        <v>637.7165976462888</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O26" t="n">
-        <v>843.247869574119</v>
+        <v>110.4553161506355</v>
       </c>
       <c r="P26" t="n">
-        <v>773.2870600407081</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q26" t="n">
-        <v>615.8520732695737</v>
+        <v>172.8226843274854</v>
       </c>
       <c r="R26" t="n">
         <v>294.54111633436</v>
@@ -10100,13 +10100,13 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>314.0531751575203</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>1060.271045550332</v>
+        <v>657.4491031847533</v>
       </c>
       <c r="N29" t="n">
         <v>1096.663422488788</v>
@@ -10346,10 +10346,10 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N32" t="n">
-        <v>698.9556687269011</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O32" t="n">
-        <v>843.2478695741336</v>
+        <v>445.5401158122483</v>
       </c>
       <c r="P32" t="n">
         <v>773.2870600407226</v>
@@ -10574,7 +10574,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K35" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -10586,13 +10586,13 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O35" t="n">
-        <v>843.2478695741409</v>
+        <v>70.24786957409245</v>
       </c>
       <c r="P35" t="n">
-        <v>773.2870600407299</v>
+        <v>431.7041887557771</v>
       </c>
       <c r="Q35" t="n">
-        <v>218.1443195076731</v>
+        <v>615.8520732695737</v>
       </c>
       <c r="R35" t="n">
         <v>294.54111633436</v>
@@ -10811,7 +10811,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K38" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L38" t="n">
         <v>0</v>
@@ -10823,10 +10823,10 @@
         <v>1096.663422488788</v>
       </c>
       <c r="O38" t="n">
-        <v>445.5401158122395</v>
+        <v>24.35580165002573</v>
       </c>
       <c r="P38" t="n">
-        <v>773.2870600407372</v>
+        <v>477.5962566798451</v>
       </c>
       <c r="Q38" t="n">
         <v>615.8520732695737</v>
@@ -11048,7 +11048,7 @@
         <v>430.3047365861567</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>314.0531751574913</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -11057,13 +11057,13 @@
         <v>1060.271045550332</v>
       </c>
       <c r="N41" t="n">
-        <v>637.7165976462162</v>
+        <v>1096.663422488788</v>
       </c>
       <c r="O41" t="n">
         <v>843.2478695741554</v>
       </c>
       <c r="P41" t="n">
-        <v>773.2870600407444</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q41" t="n">
         <v>615.8520732695737</v>
@@ -11285,10 +11285,10 @@
         <v>35.04300624509033</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>709.3149054985431</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>1060.271045550332</v>
@@ -11300,7 +11300,7 @@
         <v>70.24786957409245</v>
       </c>
       <c r="P44" t="n">
-        <v>773.287060040759</v>
+        <v>0.2870600406814136</v>
       </c>
       <c r="Q44" t="n">
         <v>615.8520732695737</v>
@@ -22700,7 +22700,7 @@
         <v>0</v>
       </c>
       <c r="L4" t="n">
-        <v>23.54762815777917</v>
+        <v>0</v>
       </c>
       <c r="M4" t="n">
         <v>0</v>
@@ -22718,7 +22718,7 @@
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>5.662449696455099</v>
+        <v>29.21007785422916</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -22940,7 +22940,7 @@
         <v>23.54762815777917</v>
       </c>
       <c r="M7" t="n">
-        <v>5.662449696447268</v>
+        <v>5.662449696446146</v>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -23174,10 +23174,10 @@
         <v>0</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>23.54762815777917</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>5.662449696453123</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -23192,7 +23192,7 @@
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>29.21007785422279</v>
+        <v>0</v>
       </c>
       <c r="S10" t="n">
         <v>0</v>
@@ -23226,22 +23226,22 @@
         <v>0</v>
       </c>
       <c r="C11" t="n">
-        <v>0</v>
+        <v>122.4859127853972</v>
       </c>
       <c r="D11" t="n">
-        <v>35.41065930916159</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E11" t="n">
-        <v>179.3632896068686</v>
+        <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>179.8896287080119</v>
+        <v>0</v>
       </c>
       <c r="G11" t="n">
         <v>178.7573722870162</v>
       </c>
       <c r="H11" t="n">
-        <v>183.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
         <v>0</v>
@@ -23274,7 +23274,7 @@
         <v>25.87859882829446</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>269.8481678023229</v>
       </c>
       <c r="T11" t="n">
         <v>0</v>
@@ -23426,10 +23426,10 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q13" t="n">
-        <v>160.0624669370703</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R13" t="n">
-        <v>501.6021279811511</v>
+        <v>160.8253284926234</v>
       </c>
       <c r="S13" t="n">
         <v>137.3734797028554</v>
@@ -23469,16 +23469,16 @@
         <v>0</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>153.3632896068686</v>
       </c>
       <c r="F14" t="n">
-        <v>82.66357762404179</v>
+        <v>86.30994672070055</v>
       </c>
       <c r="G14" t="n">
         <v>152.7573722870162</v>
       </c>
       <c r="H14" t="n">
-        <v>157.0096587035274</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
@@ -23654,19 +23654,19 @@
         <v>269.6316114025499</v>
       </c>
       <c r="N16" t="n">
-        <v>181.0500921949918</v>
+        <v>320.1850752716849</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>389.445564079015</v>
       </c>
       <c r="P16" t="n">
         <v>436.4478973282775</v>
       </c>
       <c r="Q16" t="n">
-        <v>474.839266425598</v>
+        <v>421.860847251041</v>
       </c>
       <c r="R16" t="n">
-        <v>475.6021279811511</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>111.3734797028554</v>
@@ -23712,7 +23712,7 @@
         <v>0</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>0.4306086145860206</v>
       </c>
       <c r="H17" t="n">
         <v>0</v>
@@ -23748,7 +23748,7 @@
         <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
         <v>0</v>
@@ -23897,13 +23897,13 @@
         <v>361.445564079015</v>
       </c>
       <c r="P19" t="n">
-        <v>408.4478973282775</v>
+        <v>69.04626797189979</v>
       </c>
       <c r="Q19" t="n">
-        <v>108.2004986247733</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>447.6021279811511</v>
       </c>
       <c r="S19" t="n">
         <v>83.37347970285543</v>
@@ -23985,7 +23985,7 @@
         <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.430608614585708</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
         <v>0</v>
@@ -23997,7 +23997,7 @@
         <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.4306086145857648</v>
       </c>
       <c r="X20" t="n">
         <v>0</v>
@@ -24131,16 +24131,16 @@
         <v>292.1850752716849</v>
       </c>
       <c r="O22" t="n">
-        <v>22.80679627819029</v>
+        <v>361.445564079015</v>
       </c>
       <c r="P22" t="n">
         <v>408.4478973282775</v>
       </c>
       <c r="Q22" t="n">
-        <v>446.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>108.2004986247733</v>
       </c>
       <c r="S22" t="n">
         <v>83.37347970285543</v>
@@ -24222,7 +24222,7 @@
         <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>0.430608614585708</v>
       </c>
       <c r="T23" t="n">
         <v>0</v>
@@ -24234,7 +24234,7 @@
         <v>0</v>
       </c>
       <c r="W23" t="n">
-        <v>0.4306086145857648</v>
+        <v>0</v>
       </c>
       <c r="X23" t="n">
         <v>0</v>
@@ -24329,16 +24329,16 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0</v>
+        <v>8.113800337078658</v>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0</v>
+        <v>6.53621805555548</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>1.98090483695654</v>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -24356,31 +24356,31 @@
         <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>9.520773801143037</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>34.53793813736451</v>
+        <v>0</v>
       </c>
       <c r="N25" t="n">
-        <v>292.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O25" t="n">
         <v>361.445564079015</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>408.4478973282775</v>
       </c>
       <c r="Q25" t="n">
         <v>446.839266425598</v>
       </c>
       <c r="R25" t="n">
-        <v>447.6021279811511</v>
+        <v>423.0990267340447</v>
       </c>
       <c r="S25" t="n">
-        <v>83.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T25" t="n">
         <v>0</v>
@@ -24414,19 +24414,19 @@
         <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>0</v>
+        <v>185.3391557398498</v>
       </c>
       <c r="E26" t="n">
-        <v>179.3632896068686</v>
+        <v>107.9983880296801</v>
       </c>
       <c r="F26" t="n">
         <v>0</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>178.7573722870162</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>183.0096587035274</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
@@ -24465,10 +24465,10 @@
         <v>0</v>
       </c>
       <c r="U26" t="n">
-        <v>357.2076936691875</v>
+        <v>0</v>
       </c>
       <c r="V26" t="n">
-        <v>404.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W26" t="n">
         <v>0</v>
@@ -24477,7 +24477,7 @@
         <v>0</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>286.3174326828064</v>
       </c>
     </row>
     <row r="27">
@@ -24599,7 +24599,7 @@
         <v>198.5476281577792</v>
       </c>
       <c r="M28" t="n">
-        <v>295.6316114025499</v>
+        <v>92.22829161687761</v>
       </c>
       <c r="N28" t="n">
         <v>346.1850752716849</v>
@@ -24611,13 +24611,13 @@
         <v>462.4478973282775</v>
       </c>
       <c r="Q28" t="n">
-        <v>158.6896570983607</v>
+        <v>500.839266425598</v>
       </c>
       <c r="R28" t="n">
         <v>501.6021279811511</v>
       </c>
       <c r="S28" t="n">
-        <v>137.3734797028554</v>
+        <v>0</v>
       </c>
       <c r="T28" t="n">
         <v>0</v>
@@ -24629,7 +24629,7 @@
         <v>0</v>
       </c>
       <c r="W28" t="n">
-        <v>1.372809838709685</v>
+        <v>0</v>
       </c>
       <c r="X28" t="n">
         <v>22.44364543010755</v>
@@ -24645,10 +24645,10 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>220.4020581374557</v>
+        <v>0</v>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>224.4745782429939</v>
       </c>
       <c r="D29" t="n">
         <v>0</v>
@@ -24663,7 +24663,7 @@
         <v>178.7573722870162</v>
       </c>
       <c r="H29" t="n">
-        <v>183.0096587035274</v>
+        <v>178.9371385979892</v>
       </c>
       <c r="I29" t="n">
         <v>0</v>
@@ -24839,13 +24839,13 @@
         <v>295.6316114025499</v>
       </c>
       <c r="N31" t="n">
-        <v>346.1850752716849</v>
+        <v>5.408275783157251</v>
       </c>
       <c r="O31" t="n">
         <v>415.445564079015</v>
       </c>
       <c r="P31" t="n">
-        <v>121.6710978397498</v>
+        <v>462.4478973282775</v>
       </c>
       <c r="Q31" t="n">
         <v>500.839266425598</v>
@@ -25079,13 +25079,13 @@
         <v>280.1850752716849</v>
       </c>
       <c r="O34" t="n">
-        <v>349.445564079015</v>
+        <v>0</v>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q34" t="n">
-        <v>397.7708462434862</v>
+        <v>350.7685129942237</v>
       </c>
       <c r="R34" t="n">
         <v>0</v>
@@ -25307,28 +25307,28 @@
         <v>0</v>
       </c>
       <c r="L37" t="n">
-        <v>132.5476281577792</v>
+        <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>229.6316114025499</v>
+        <v>0</v>
       </c>
       <c r="N37" t="n">
-        <v>280.1850752716849</v>
+        <v>0</v>
       </c>
       <c r="O37" t="n">
-        <v>349.445564079015</v>
+        <v>122.6914334194885</v>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>396.4478973282775</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>434.839266425598</v>
       </c>
       <c r="R37" t="n">
-        <v>326.3973665406309</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S37" t="n">
-        <v>71.37347970285543</v>
+        <v>0</v>
       </c>
       <c r="T37" t="n">
         <v>0</v>
@@ -25547,22 +25547,22 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>0</v>
+        <v>229.6316114025499</v>
       </c>
       <c r="N40" t="n">
-        <v>208.8479973215976</v>
+        <v>280.1850752716849</v>
       </c>
       <c r="O40" t="n">
         <v>349.445564079015</v>
       </c>
       <c r="P40" t="n">
-        <v>396.4478973282775</v>
+        <v>94.71634642011435</v>
       </c>
       <c r="Q40" t="n">
-        <v>434.839266425598</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>435.6021279811511</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -25593,25 +25593,25 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0</v>
+        <v>268.9993129555745</v>
       </c>
       <c r="C41" t="n">
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0</v>
+        <v>83.40274518188112</v>
       </c>
       <c r="E41" t="n">
-        <v>0</v>
+        <v>191.3632896068686</v>
       </c>
       <c r="F41" t="n">
-        <v>0</v>
+        <v>191.8896287080119</v>
       </c>
       <c r="G41" t="n">
         <v>190.7573722870162</v>
       </c>
       <c r="H41" t="n">
-        <v>0</v>
+        <v>195.0096587035274</v>
       </c>
       <c r="I41" t="n">
         <v>0</v>
@@ -25641,22 +25641,22 @@
         <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>37.87859882829446</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
       </c>
       <c r="T41" t="n">
-        <v>50.561536179798</v>
+        <v>0</v>
       </c>
       <c r="U41" t="n">
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>416.8510241668239</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>425.3734759809475</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>0</v>
@@ -25735,7 +25735,7 @@
         <v>0</v>
       </c>
       <c r="W42" t="n">
-        <v>219.3731429098285</v>
+        <v>137.4664427423195</v>
       </c>
       <c r="X42" t="n">
         <v>0</v>
@@ -25799,7 +25799,7 @@
         <v>512.839266425598</v>
       </c>
       <c r="R43" t="n">
-        <v>368.900291018552</v>
+        <v>513.6021279811511</v>
       </c>
       <c r="S43" t="n">
         <v>149.3734797028554</v>
@@ -25830,10 +25830,10 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>152.588324154612</v>
+        <v>0</v>
       </c>
       <c r="C44" t="n">
-        <v>262.4745782429939</v>
+        <v>0</v>
       </c>
       <c r="D44" t="n">
         <v>223.3391557398498</v>
@@ -25881,7 +25881,7 @@
         <v>0</v>
       </c>
       <c r="S44" t="n">
-        <v>0</v>
+        <v>307.8481678023229</v>
       </c>
       <c r="T44" t="n">
         <v>0</v>
@@ -25896,7 +25896,7 @@
         <v>0</v>
       </c>
       <c r="X44" t="n">
-        <v>0</v>
+        <v>107.2147345952831</v>
       </c>
       <c r="Y44" t="n">
         <v>0</v>
@@ -25912,16 +25912,16 @@
         <v>0</v>
       </c>
       <c r="C45" t="n">
-        <v>65.45222128918327</v>
+        <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>160.9376868977026</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
-        <v>155.6720972219126</v>
+        <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>152.6362423378769</v>
+        <v>0</v>
       </c>
       <c r="G45" t="n">
         <v>138.7395358750273</v>
@@ -25930,7 +25930,7 @@
         <v>145.1680871864211</v>
       </c>
       <c r="I45" t="n">
-        <v>30.12638589134853</v>
+        <v>0</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
@@ -25957,10 +25957,10 @@
         <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>36.16508545463461</v>
       </c>
       <c r="S45" t="n">
-        <v>0</v>
+        <v>279.5639999646113</v>
       </c>
       <c r="T45" t="n">
         <v>0</v>
@@ -25972,7 +25972,7 @@
         <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>245.3731429098285</v>
       </c>
       <c r="X45" t="n">
         <v>0</v>
@@ -26006,7 +26006,7 @@
         <v>58.04387284153003</v>
       </c>
       <c r="H46" t="n">
-        <v>0</v>
+        <v>41.77112610161862</v>
       </c>
       <c r="I46" t="n">
         <v>0</v>
@@ -26042,13 +26042,13 @@
         <v>175.3734797028554</v>
       </c>
       <c r="T46" t="n">
-        <v>23.02456650625771</v>
+        <v>0</v>
       </c>
       <c r="U46" t="n">
         <v>0</v>
       </c>
       <c r="V46" t="n">
-        <v>12.17031021621619</v>
+        <v>0</v>
       </c>
       <c r="W46" t="n">
         <v>0</v>
@@ -26086,7 +26086,7 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>932501.55644014</v>
+        <v>932501.5564401401</v>
       </c>
     </row>
     <row r="3">
@@ -26142,7 +26142,7 @@
         <v>7</v>
       </c>
       <c r="B9" t="n">
-        <v>6438648.942598144</v>
+        <v>6438648.942598143</v>
       </c>
     </row>
     <row r="10">
@@ -26150,7 +26150,7 @@
         <v>8</v>
       </c>
       <c r="B10" t="n">
-        <v>7159427.740302745</v>
+        <v>7159427.740302742</v>
       </c>
     </row>
     <row r="11">
@@ -26158,7 +26158,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="n">
-        <v>7883114.108916435</v>
+        <v>7883114.108916434</v>
       </c>
     </row>
     <row r="12">
@@ -26174,7 +26174,7 @@
         <v>11</v>
       </c>
       <c r="B13" t="n">
-        <v>9478046.134487042</v>
+        <v>9478046.13448704</v>
       </c>
     </row>
     <row r="14">
@@ -26198,7 +26198,7 @@
         <v>14</v>
       </c>
       <c r="B16" t="n">
-        <v>11630813.78447765</v>
+        <v>11630813.78447764</v>
       </c>
     </row>
   </sheetData>
@@ -26272,10 +26272,10 @@
         <v>1384543.598310502</v>
       </c>
       <c r="C2" t="n">
+        <v>1384543.598310503</v>
+      </c>
+      <c r="D2" t="n">
         <v>1384543.598310502</v>
-      </c>
-      <c r="D2" t="n">
-        <v>1384543.598310503</v>
       </c>
       <c r="E2" t="n">
         <v>1238631.925191176</v>
@@ -26284,7 +26284,7 @@
         <v>1289145.384725367</v>
       </c>
       <c r="G2" t="n">
-        <v>1341071.591838157</v>
+        <v>1341071.591838156</v>
       </c>
       <c r="H2" t="n">
         <v>1341071.591838156</v>
@@ -26305,10 +26305,10 @@
         <v>1348629.813221775</v>
       </c>
       <c r="N2" t="n">
-        <v>1348629.813221776</v>
+        <v>1348629.813221775</v>
       </c>
       <c r="O2" t="n">
-        <v>1188145.666027177</v>
+        <v>1188145.666027176</v>
       </c>
       <c r="P2" t="n">
         <v>1108225.883718743</v>
@@ -26373,49 +26373,49 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>556224.1964558328</v>
+        <v>551386.5909530218</v>
       </c>
       <c r="C4" t="n">
-        <v>554472.2877165733</v>
+        <v>549634.6822137623</v>
       </c>
       <c r="D4" t="n">
-        <v>552718.0024037627</v>
+        <v>547880.3969009514</v>
       </c>
       <c r="E4" t="n">
-        <v>474694.9568742209</v>
+        <v>469906.9358754652</v>
       </c>
       <c r="F4" t="n">
-        <v>498969.5726682165</v>
+        <v>494181.551669461</v>
       </c>
       <c r="G4" t="n">
-        <v>523758.9807925398</v>
+        <v>518970.9597937841</v>
       </c>
       <c r="H4" t="n">
-        <v>522086.0458524426</v>
+        <v>517298.0248536869</v>
       </c>
       <c r="I4" t="n">
-        <v>520410.7754680158</v>
+        <v>515622.7544692601</v>
       </c>
       <c r="J4" t="n">
-        <v>464369.6125335261</v>
+        <v>459704.5839768919</v>
       </c>
       <c r="K4" t="n">
-        <v>462904.8708795845</v>
+        <v>458239.8423229501</v>
       </c>
       <c r="L4" t="n">
-        <v>524533.9144927659</v>
+        <v>519822.4908174383</v>
       </c>
       <c r="M4" t="n">
-        <v>522803.7957912134</v>
+        <v>518092.3721158857</v>
       </c>
       <c r="N4" t="n">
-        <v>521071.1894666618</v>
+        <v>516359.7657913335</v>
       </c>
       <c r="O4" t="n">
-        <v>438916.084163369</v>
+        <v>434251.0556067348</v>
       </c>
       <c r="P4" t="n">
-        <v>398110.3467682331</v>
+        <v>393445.3182115989</v>
       </c>
     </row>
     <row r="5">
@@ -26477,49 +26477,49 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>458672.6018546697</v>
+        <v>463510.2073574807</v>
       </c>
       <c r="C6" t="n">
-        <v>746952.5105939286</v>
+        <v>751790.1160967408</v>
       </c>
       <c r="D6" t="n">
-        <v>748706.7959067402</v>
+        <v>753544.4014095506</v>
       </c>
       <c r="E6" t="n">
-        <v>515530.2433169553</v>
+        <v>520318.264315711</v>
       </c>
       <c r="F6" t="n">
-        <v>698783.2930571507</v>
+        <v>703571.3140559065</v>
       </c>
       <c r="G6" t="n">
-        <v>721966.1600456168</v>
+        <v>726754.1810443723</v>
       </c>
       <c r="H6" t="n">
-        <v>746039.0949857136</v>
+        <v>750827.1159844695</v>
       </c>
       <c r="I6" t="n">
-        <v>747714.3653701408</v>
+        <v>752502.3863688967</v>
       </c>
       <c r="J6" t="n">
-        <v>285520.4708896498</v>
+        <v>290185.499446284</v>
       </c>
       <c r="K6" t="n">
-        <v>675081.2125435916</v>
+        <v>679746.2411002258</v>
       </c>
       <c r="L6" t="n">
-        <v>677433.419729009</v>
+        <v>682144.8434043368</v>
       </c>
       <c r="M6" t="n">
-        <v>754363.538430562</v>
+        <v>759074.9621058893</v>
       </c>
       <c r="N6" t="n">
-        <v>756096.1447551141</v>
+        <v>760807.5684304417</v>
       </c>
       <c r="O6" t="n">
-        <v>609924.4848638079</v>
+        <v>614589.5134204412</v>
       </c>
       <c r="P6" t="n">
-        <v>647396.2339505102</v>
+        <v>652061.2625071444</v>
       </c>
     </row>
   </sheetData>
@@ -26993,7 +26993,7 @@
         <v>-0</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J2" t="n">
         <v>171</v>
@@ -27008,7 +27008,7 @@
         <v>-0</v>
       </c>
       <c r="N2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
         <v>93</v>
@@ -27024,7 +27024,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="C3" t="n">
         <v>-0</v>
@@ -27436,25 +27436,25 @@
         <v>400</v>
       </c>
       <c r="C2" t="n">
+        <v>0</v>
+      </c>
+      <c r="D2" t="n">
         <v>400</v>
       </c>
-      <c r="D2" t="n">
-        <v>0</v>
-      </c>
       <c r="E2" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
         <v>400</v>
       </c>
       <c r="G2" t="n">
+        <v>307.3903671255647</v>
+      </c>
+      <c r="H2" t="n">
         <v>400</v>
       </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
       <c r="I2" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J2" t="n">
         <v>0</v>
@@ -27481,7 +27481,7 @@
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S2" t="n">
         <v>400</v>
@@ -27496,13 +27496,13 @@
         <v>400</v>
       </c>
       <c r="W2" t="n">
-        <v>306.4306086145855</v>
+        <v>400</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
     </row>
     <row r="3">
@@ -27512,10 +27512,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C3" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D3" t="n">
         <v>347.9376868977026</v>
@@ -27530,7 +27530,7 @@
         <v>325.7395358750273</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>332.1680871864211</v>
       </c>
       <c r="I3" t="n">
         <v>217.1263858913485</v>
@@ -27557,13 +27557,13 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>32.07828453980446</v>
+        <v>173.0792650904796</v>
       </c>
       <c r="R3" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>400</v>
+        <v>303.3742880620964</v>
       </c>
       <c r="T3" t="n">
         <v>400</v>
@@ -27591,7 +27591,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>400</v>
+        <v>287.1138003370787</v>
       </c>
       <c r="C4" t="n">
         <v>400</v>
@@ -27606,19 +27606,19 @@
         <v>400</v>
       </c>
       <c r="G4" t="n">
-        <v>245.04387284153</v>
+        <v>400</v>
       </c>
       <c r="H4" t="n">
-        <v>228.7711261016186</v>
+        <v>400</v>
       </c>
       <c r="I4" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J4" t="n">
         <v>35.26894883590776</v>
       </c>
       <c r="K4" t="n">
-        <v>372.0506390287607</v>
+        <v>309.8421732000279</v>
       </c>
       <c r="L4" t="n">
         <v>400</v>
@@ -27651,10 +27651,10 @@
         <v>400</v>
       </c>
       <c r="V4" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W4" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X4" t="n">
         <v>247.4436454301076</v>
@@ -27676,19 +27676,19 @@
         <v>400</v>
       </c>
       <c r="D5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>56.51176829727075</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
         <v>400</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
@@ -27721,10 +27721,10 @@
         <v>250.8785988282945</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>56.51176829727007</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="U5" t="n">
         <v>400</v>
@@ -27749,19 +27749,19 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>384.5565566463266</v>
+        <v>235.8685316061258</v>
       </c>
       <c r="C6" t="n">
-        <v>361.0999124455193</v>
+        <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>172.5204020740694</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>342.6720972219126</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>339.6362423378769</v>
       </c>
       <c r="G6" t="n">
         <v>325.7395358750273</v>
@@ -27846,13 +27846,13 @@
         <v>400</v>
       </c>
       <c r="H7" t="n">
-        <v>331.2709046696284</v>
+        <v>400</v>
       </c>
       <c r="I7" t="n">
-        <v>176.6334556201183</v>
+        <v>400</v>
       </c>
       <c r="J7" t="n">
-        <v>35.26894883590776</v>
+        <v>270.1865436406219</v>
       </c>
       <c r="K7" t="n">
         <v>288.520773801143</v>
@@ -27888,13 +27888,13 @@
         <v>150.9583912744579</v>
       </c>
       <c r="V7" t="n">
-        <v>400</v>
+        <v>199.1703102162162</v>
       </c>
       <c r="W7" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X7" t="n">
-        <v>400</v>
+        <v>247.4436454301076</v>
       </c>
       <c r="Y7" t="n">
         <v>400</v>
@@ -27916,19 +27916,19 @@
         <v>400</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="F8" t="n">
         <v>400</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="I8" t="n">
-        <v>150.0811596826846</v>
+        <v>0</v>
       </c>
       <c r="J8" t="n">
         <v>0</v>
@@ -27955,13 +27955,13 @@
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>250.8785988282945</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>307.3903671255646</v>
       </c>
       <c r="T8" t="n">
-        <v>306.4306086145853</v>
+        <v>400</v>
       </c>
       <c r="U8" t="n">
         <v>400</v>
@@ -27970,13 +27970,13 @@
         <v>400</v>
       </c>
       <c r="W8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>400</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -27986,13 +27986,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0</v>
+        <v>384.5565566463266</v>
       </c>
       <c r="C9" t="n">
-        <v>287.9308447084231</v>
+        <v>361.0999124455193</v>
       </c>
       <c r="D9" t="n">
-        <v>347.9376868977026</v>
+        <v>289.6034552804142</v>
       </c>
       <c r="E9" t="n">
         <v>342.6720972219126</v>
@@ -28055,7 +28055,7 @@
         <v>0</v>
       </c>
       <c r="Y9" t="n">
-        <v>399.3913927661343</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -28074,10 +28074,10 @@
         <v>285.5362180555555</v>
       </c>
       <c r="E10" t="n">
-        <v>400</v>
+        <v>280.9809048369565</v>
       </c>
       <c r="F10" t="n">
-        <v>400</v>
+        <v>274.3828559677419</v>
       </c>
       <c r="G10" t="n">
         <v>400</v>
@@ -28089,7 +28089,7 @@
         <v>400</v>
       </c>
       <c r="J10" t="n">
-        <v>35.26894883590776</v>
+        <v>80.49503929616792</v>
       </c>
       <c r="K10" t="n">
         <v>400</v>
@@ -28122,19 +28122,19 @@
         <v>400</v>
       </c>
       <c r="U10" t="n">
-        <v>340.3269980379992</v>
+        <v>400</v>
       </c>
       <c r="V10" t="n">
-        <v>199.1703102162162</v>
+        <v>400</v>
       </c>
       <c r="W10" t="n">
-        <v>400</v>
+        <v>226.3728098387097</v>
       </c>
       <c r="X10" t="n">
         <v>247.4436454301076</v>
       </c>
       <c r="Y10" t="n">
-        <v>287.4653528494624</v>
+        <v>400</v>
       </c>
     </row>
     <row r="11">
@@ -28253,7 +28253,7 @@
         <v>225</v>
       </c>
       <c r="L12" t="n">
-        <v>225</v>
+        <v>19.1168712588389</v>
       </c>
       <c r="M12" t="n">
         <v>225</v>
@@ -28265,7 +28265,7 @@
         <v>225</v>
       </c>
       <c r="P12" t="n">
-        <v>19.11687125883863</v>
+        <v>225</v>
       </c>
       <c r="Q12" t="n">
         <v>225</v>
@@ -28484,13 +28484,13 @@
         <v>251</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>166.1982915220773</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>251</v>
       </c>
       <c r="L15" t="n">
-        <v>251</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
         <v>251</v>
@@ -28499,7 +28499,7 @@
         <v>0</v>
       </c>
       <c r="O15" t="n">
-        <v>166.1982915220774</v>
+        <v>0</v>
       </c>
       <c r="P15" t="n">
         <v>251</v>
@@ -28718,31 +28718,31 @@
         <v>279</v>
       </c>
       <c r="I18" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" t="n">
+        <v>217.5442043757546</v>
+      </c>
+      <c r="P18" t="n">
         <v>279</v>
       </c>
-      <c r="J18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" t="n">
+      <c r="Q18" t="n">
         <v>279</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="n">
-        <v>261.5913251766236</v>
-      </c>
-      <c r="O18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R18" t="n">
         <v>279</v>
@@ -28955,28 +28955,28 @@
         <v>279</v>
       </c>
       <c r="I21" t="n">
+        <v>217.1263858913485</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>217.5442043757546</v>
+      </c>
+      <c r="P21" t="n">
         <v>279</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" t="n">
-        <v>279</v>
-      </c>
-      <c r="P21" t="n">
-        <v>155.6705902671032</v>
       </c>
       <c r="Q21" t="n">
         <v>279</v>
@@ -29207,16 +29207,16 @@
         <v>0</v>
       </c>
       <c r="N24" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" t="n">
+        <v>217.5442043757546</v>
+      </c>
+      <c r="P24" t="n">
         <v>279</v>
       </c>
-      <c r="O24" t="n">
+      <c r="Q24" t="n">
         <v>279</v>
-      </c>
-      <c r="P24" t="n">
-        <v>44.46493928527515</v>
-      </c>
-      <c r="Q24" t="n">
-        <v>173.0792650904796</v>
       </c>
       <c r="R24" t="n">
         <v>279</v>
@@ -29429,10 +29429,10 @@
         <v>225</v>
       </c>
       <c r="I27" t="n">
-        <v>217.1263858913485</v>
+        <v>225</v>
       </c>
       <c r="J27" t="n">
-        <v>26.99048536749061</v>
+        <v>225</v>
       </c>
       <c r="K27" t="n">
         <v>225</v>
@@ -29441,7 +29441,7 @@
         <v>225</v>
       </c>
       <c r="M27" t="n">
-        <v>225</v>
+        <v>19.11687125883903</v>
       </c>
       <c r="N27" t="n">
         <v>225</v>
@@ -29669,10 +29669,10 @@
         <v>225</v>
       </c>
       <c r="J30" t="n">
-        <v>19.11687125883917</v>
+        <v>225</v>
       </c>
       <c r="K30" t="n">
-        <v>225</v>
+        <v>19.11687125883918</v>
       </c>
       <c r="L30" t="n">
         <v>225</v>
@@ -29906,28 +29906,28 @@
         <v>291</v>
       </c>
       <c r="J33" t="n">
-        <v>0</v>
+        <v>227.015861157829</v>
       </c>
       <c r="K33" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" t="n">
+        <v>0</v>
+      </c>
+      <c r="P33" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="n">
         <v>291</v>
-      </c>
-      <c r="L33" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" t="n">
-        <v>0</v>
-      </c>
-      <c r="P33" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q33" t="n">
-        <v>227.0158611578291</v>
       </c>
       <c r="R33" t="n">
         <v>291</v>
@@ -30058,7 +30058,7 @@
         <v>291</v>
       </c>
       <c r="H35" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="I35" t="n">
         <v>150.0811596826846</v>
@@ -30088,7 +30088,7 @@
         <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S35" t="n">
         <v>291</v>
@@ -30158,13 +30158,13 @@
         <v>0</v>
       </c>
       <c r="O36" t="n">
-        <v>0</v>
+        <v>227.0158611578287</v>
       </c>
       <c r="P36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="n">
         <v>291</v>
-      </c>
-      <c r="Q36" t="n">
-        <v>227.0158611578289</v>
       </c>
       <c r="R36" t="n">
         <v>291</v>
@@ -30295,7 +30295,7 @@
         <v>291</v>
       </c>
       <c r="H38" t="n">
-        <v>282.5434086145858</v>
+        <v>291</v>
       </c>
       <c r="I38" t="n">
         <v>150.0811596826846</v>
@@ -30325,7 +30325,7 @@
         <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>250.8785988282945</v>
+        <v>242.4220074428797</v>
       </c>
       <c r="S38" t="n">
         <v>291</v>
@@ -30380,7 +30380,7 @@
         <v>291</v>
       </c>
       <c r="J39" t="n">
-        <v>227.015861157829</v>
+        <v>0</v>
       </c>
       <c r="K39" t="n">
         <v>0</v>
@@ -30392,7 +30392,7 @@
         <v>0</v>
       </c>
       <c r="N39" t="n">
-        <v>0</v>
+        <v>227.0158611578289</v>
       </c>
       <c r="O39" t="n">
         <v>0</v>
@@ -30501,7 +30501,7 @@
         <v>291</v>
       </c>
       <c r="X40" t="n">
-        <v>291.0000000000276</v>
+        <v>291</v>
       </c>
       <c r="Y40" t="n">
         <v>291</v>
@@ -30632,10 +30632,10 @@
         <v>213</v>
       </c>
       <c r="O42" t="n">
+        <v>158.5978143635411</v>
+      </c>
+      <c r="P42" t="n">
         <v>213</v>
-      </c>
-      <c r="P42" t="n">
-        <v>75.02807641077207</v>
       </c>
       <c r="Q42" t="n">
         <v>213</v>
@@ -30693,10 +30693,10 @@
         <v>213</v>
       </c>
       <c r="I43" t="n">
-        <v>213</v>
+        <v>206.3691315106685</v>
       </c>
       <c r="J43" t="n">
-        <v>176.2779507298015</v>
+        <v>35.26894883590776</v>
       </c>
       <c r="K43" t="n">
         <v>213</v>
@@ -30857,7 +30857,7 @@
         <v>187</v>
       </c>
       <c r="K45" t="n">
-        <v>39.33690837726046</v>
+        <v>187</v>
       </c>
       <c r="L45" t="n">
         <v>187</v>
@@ -30866,7 +30866,7 @@
         <v>187</v>
       </c>
       <c r="N45" t="n">
-        <v>187</v>
+        <v>43.13489359198327</v>
       </c>
       <c r="O45" t="n">
         <v>187</v>
@@ -30933,7 +30933,7 @@
         <v>176.6334556201183</v>
       </c>
       <c r="J46" t="n">
-        <v>118.0604353580262</v>
+        <v>111.3506614786826</v>
       </c>
       <c r="K46" t="n">
         <v>187</v>
@@ -34749,7 +34749,7 @@
         <v>814.0000000000001</v>
       </c>
       <c r="L2" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>814</v>
@@ -34877,7 +34877,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>112.8861996629213</v>
+        <v>0</v>
       </c>
       <c r="C4" t="n">
         <v>127.2747533519553</v>
@@ -34892,19 +34892,19 @@
         <v>125.6171440322581</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>154.95612715847</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>83.52986522761768</v>
+        <v>21.32139939888486</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -34937,10 +34937,10 @@
         <v>249.0416087255421</v>
       </c>
       <c r="V4" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -34980,7 +34980,7 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>814.0000000000036</v>
+        <v>814</v>
       </c>
       <c r="K5" t="n">
         <v>814</v>
@@ -34992,7 +34992,7 @@
         <v>814</v>
       </c>
       <c r="N5" t="n">
-        <v>814</v>
+        <v>814.0000000000036</v>
       </c>
       <c r="O5" t="n">
         <v>814</v>
@@ -35132,13 +35132,13 @@
         <v>154.95612715847</v>
       </c>
       <c r="H7" t="n">
-        <v>102.4997785680098</v>
+        <v>171.2288738983814</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>223.3665443798817</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>234.9175948047142</v>
       </c>
       <c r="K7" t="n">
         <v>0</v>
@@ -35174,13 +35174,13 @@
         <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>200.8296897837838</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>152.5563545698924</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>112.5346471505376</v>
@@ -35220,7 +35220,7 @@
         <v>814</v>
       </c>
       <c r="K8" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>814</v>
@@ -35235,7 +35235,7 @@
         <v>814</v>
       </c>
       <c r="P8" t="n">
-        <v>814.0000000000045</v>
+        <v>814</v>
       </c>
       <c r="Q8" t="n">
         <v>814</v>
@@ -35360,10 +35360,10 @@
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>119.0190951630435</v>
+        <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>125.6171440322581</v>
+        <v>0</v>
       </c>
       <c r="G10" t="n">
         <v>154.95612715847</v>
@@ -35375,7 +35375,7 @@
         <v>223.3665443798817</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>45.22609046026015</v>
       </c>
       <c r="K10" t="n">
         <v>111.479226198857</v>
@@ -35408,19 +35408,19 @@
         <v>189.9754334937423</v>
       </c>
       <c r="U10" t="n">
-        <v>189.3686067635413</v>
+        <v>249.0416087255421</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>200.8296897837838</v>
       </c>
       <c r="W10" t="n">
-        <v>173.6271901612903</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>112.5346471505376</v>
       </c>
     </row>
     <row r="11">
@@ -35460,7 +35460,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L11" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
         <v>516.0089179080152</v>
@@ -35469,7 +35469,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P11" t="n">
         <v>0</v>
@@ -35539,7 +35539,7 @@
         <v>416.1038546407913</v>
       </c>
       <c r="L12" t="n">
-        <v>499.091375348687</v>
+        <v>293.2082466075259</v>
       </c>
       <c r="M12" t="n">
         <v>311.9500421645043</v>
@@ -35551,7 +35551,7 @@
         <v>466.4570219027464</v>
       </c>
       <c r="P12" t="n">
-        <v>132.7828757734918</v>
+        <v>338.6660045146532</v>
       </c>
       <c r="Q12" t="n">
         <v>51.92073490952041</v>
@@ -35697,7 +35697,7 @@
         <v>716.8751175230993</v>
       </c>
       <c r="L14" t="n">
-        <v>532.5214919778891</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>516.0089179080152</v>
@@ -35706,7 +35706,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>532.5214919778892</v>
       </c>
       <c r="P14" t="n">
         <v>0</v>
@@ -35770,13 +35770,13 @@
         <v>33.87361410865147</v>
       </c>
       <c r="J15" t="n">
-        <v>125.2086062376757</v>
+        <v>291.406897759753</v>
       </c>
       <c r="K15" t="n">
-        <v>191.1038546407913</v>
+        <v>442.1038546407913</v>
       </c>
       <c r="L15" t="n">
-        <v>525.0913753486871</v>
+        <v>274.091375348687</v>
       </c>
       <c r="M15" t="n">
         <v>337.9500421645043</v>
@@ -35785,7 +35785,7 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O15" t="n">
-        <v>407.6553134248237</v>
+        <v>241.4570219027464</v>
       </c>
       <c r="P15" t="n">
         <v>364.6660045146532</v>
@@ -35928,25 +35928,25 @@
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L17" t="n">
-        <v>814</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N17" t="n">
-        <v>240.811073919941</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P17" t="n">
-        <v>814</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
         <v>443.0293889420883</v>
@@ -36004,13 +36004,13 @@
         <v>0</v>
       </c>
       <c r="I18" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J18" t="n">
         <v>125.2086062376757</v>
       </c>
       <c r="K18" t="n">
-        <v>470.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L18" t="n">
         <v>274.091375348687</v>
@@ -36019,16 +36019,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N18" t="n">
-        <v>396.2178752852784</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O18" t="n">
-        <v>241.4570219027464</v>
+        <v>459.001226278501</v>
       </c>
       <c r="P18" t="n">
-        <v>113.6660045146532</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -36165,13 +36165,13 @@
         <v>0</v>
       </c>
       <c r="J20" t="n">
-        <v>395.2617303410664</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L20" t="n">
-        <v>435.3966095009885</v>
+        <v>814.0000000000001</v>
       </c>
       <c r="M20" t="n">
         <v>516.0089179080152</v>
@@ -36180,7 +36180,7 @@
         <v>619.4144644189528</v>
       </c>
       <c r="O20" t="n">
-        <v>814</v>
+        <v>113.7832223189554</v>
       </c>
       <c r="P20" t="n">
         <v>0</v>
@@ -36241,7 +36241,7 @@
         <v>0</v>
       </c>
       <c r="I21" t="n">
-        <v>61.87361410865147</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>125.2086062376757</v>
@@ -36259,10 +36259,10 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O21" t="n">
-        <v>520.4570219027464</v>
+        <v>459.001226278501</v>
       </c>
       <c r="P21" t="n">
-        <v>269.3365947817563</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q21" t="n">
         <v>105.9207349095204</v>
@@ -36493,16 +36493,16 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N24" t="n">
-        <v>413.6265501086548</v>
+        <v>134.6265501086548</v>
       </c>
       <c r="O24" t="n">
-        <v>520.4570219027464</v>
+        <v>459.001226278501</v>
       </c>
       <c r="P24" t="n">
-        <v>158.1309437999284</v>
+        <v>392.6660045146532</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>105.9207349095204</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -36642,25 +36642,25 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>773</v>
       </c>
       <c r="M26" t="n">
         <v>516.0089179080152</v>
       </c>
       <c r="N26" t="n">
-        <v>160.4676395764535</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O26" t="n">
-        <v>773.0000000000266</v>
+        <v>40.20744657654306</v>
       </c>
       <c r="P26" t="n">
-        <v>773.0000000000266</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>443.0293889420883</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -36715,10 +36715,10 @@
         <v>0</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>7.873614108651466</v>
       </c>
       <c r="J27" t="n">
-        <v>152.1990916051663</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K27" t="n">
         <v>416.1038546407913</v>
@@ -36727,7 +36727,7 @@
         <v>499.091375348687</v>
       </c>
       <c r="M27" t="n">
-        <v>311.9500421645043</v>
+        <v>106.0669134233433</v>
       </c>
       <c r="N27" t="n">
         <v>359.6265501086548</v>
@@ -36879,13 +36879,13 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K29" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L29" t="n">
-        <v>314.0531751575203</v>
+        <v>0</v>
       </c>
       <c r="M29" t="n">
-        <v>516.0089179080152</v>
+        <v>113.186975542436</v>
       </c>
       <c r="N29" t="n">
         <v>619.4144644189528</v>
@@ -36955,10 +36955,10 @@
         <v>7.873614108651466</v>
       </c>
       <c r="J30" t="n">
-        <v>144.3254774965148</v>
+        <v>350.2086062376757</v>
       </c>
       <c r="K30" t="n">
-        <v>416.1038546407913</v>
+        <v>210.2207258996305</v>
       </c>
       <c r="L30" t="n">
         <v>499.091375348687</v>
@@ -37116,10 +37116,10 @@
         <v>773.0000000000412</v>
       </c>
       <c r="K32" t="n">
-        <v>727.10793207601</v>
+        <v>773</v>
       </c>
       <c r="L32" t="n">
-        <v>773</v>
+        <v>727.1079320760825</v>
       </c>
       <c r="M32" t="n">
         <v>773.0000000000412</v>
@@ -37192,10 +37192,10 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J33" t="n">
-        <v>125.2086062376757</v>
+        <v>352.2244673955047</v>
       </c>
       <c r="K33" t="n">
-        <v>482.1038546407913</v>
+        <v>191.1038546407913</v>
       </c>
       <c r="L33" t="n">
         <v>274.091375348687</v>
@@ -37213,7 +37213,7 @@
         <v>113.6660045146532</v>
       </c>
       <c r="Q33" t="n">
-        <v>53.93659606734953</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R33" t="n">
         <v>0</v>
@@ -37353,10 +37353,10 @@
         <v>773.0000000000484</v>
       </c>
       <c r="K35" t="n">
-        <v>727.1079320760351</v>
+        <v>727.1079320760053</v>
       </c>
       <c r="L35" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M35" t="n">
         <v>773.0000000000484</v>
@@ -37368,7 +37368,7 @@
         <v>773.0000000000484</v>
       </c>
       <c r="P35" t="n">
-        <v>773.0000000000484</v>
+        <v>773</v>
       </c>
       <c r="Q35" t="n">
         <v>773.0000000000484</v>
@@ -37444,13 +37444,13 @@
         <v>134.6265501086548</v>
       </c>
       <c r="O36" t="n">
-        <v>241.4570219027464</v>
+        <v>468.4728830605751</v>
       </c>
       <c r="P36" t="n">
-        <v>404.6660045146532</v>
+        <v>113.6660045146532</v>
       </c>
       <c r="Q36" t="n">
-        <v>53.9365960673493</v>
+        <v>117.9207349095204</v>
       </c>
       <c r="R36" t="n">
         <v>0</v>
@@ -37590,10 +37590,10 @@
         <v>773.0000000000557</v>
       </c>
       <c r="K38" t="n">
-        <v>727.1079320762731</v>
+        <v>773</v>
       </c>
       <c r="L38" t="n">
-        <v>773</v>
+        <v>772.9999999999999</v>
       </c>
       <c r="M38" t="n">
         <v>773.0000000000557</v>
@@ -37602,7 +37602,7 @@
         <v>773.0000000000557</v>
       </c>
       <c r="O38" t="n">
-        <v>773.0000000000557</v>
+        <v>727.107932075989</v>
       </c>
       <c r="P38" t="n">
         <v>773.0000000000557</v>
@@ -37666,7 +37666,7 @@
         <v>73.87361410865147</v>
       </c>
       <c r="J39" t="n">
-        <v>352.2244673955047</v>
+        <v>125.2086062376757</v>
       </c>
       <c r="K39" t="n">
         <v>191.1038546407913</v>
@@ -37678,7 +37678,7 @@
         <v>86.95004216450428</v>
       </c>
       <c r="N39" t="n">
-        <v>134.6265501086548</v>
+        <v>361.6424112664837</v>
       </c>
       <c r="O39" t="n">
         <v>241.4570219027464</v>
@@ -37787,7 +37787,7 @@
         <v>64.62719016129032</v>
       </c>
       <c r="X40" t="n">
-        <v>43.55635456992003</v>
+        <v>43.55635456989245</v>
       </c>
       <c r="Y40" t="n">
         <v>3.534647150537637</v>
@@ -37827,7 +37827,7 @@
         <v>395.2617303410664</v>
       </c>
       <c r="K41" t="n">
-        <v>0</v>
+        <v>314.0531751574913</v>
       </c>
       <c r="L41" t="n">
         <v>0</v>
@@ -37836,13 +37836,13 @@
         <v>516.0089179080152</v>
       </c>
       <c r="N41" t="n">
-        <v>160.467639576381</v>
+        <v>619.4144644189528</v>
       </c>
       <c r="O41" t="n">
         <v>773.000000000063</v>
       </c>
       <c r="P41" t="n">
-        <v>773.000000000063</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
         <v>443.0293889420883</v>
@@ -37918,10 +37918,10 @@
         <v>347.6265501086548</v>
       </c>
       <c r="O42" t="n">
-        <v>454.4570219027464</v>
+        <v>400.0548362662875</v>
       </c>
       <c r="P42" t="n">
-        <v>188.6940809254253</v>
+        <v>326.6660045146532</v>
       </c>
       <c r="Q42" t="n">
         <v>39.92073490952041</v>
@@ -37979,10 +37979,10 @@
         <v>0</v>
       </c>
       <c r="I43" t="n">
-        <v>36.36654437988173</v>
+        <v>29.73567589055027</v>
       </c>
       <c r="J43" t="n">
-        <v>141.0090018938938</v>
+        <v>0</v>
       </c>
       <c r="K43" t="n">
         <v>0</v>
@@ -38064,10 +38064,10 @@
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0</v>
+        <v>716.8751175230994</v>
       </c>
       <c r="L44" t="n">
-        <v>709.3149054985431</v>
+        <v>765.4397879755212</v>
       </c>
       <c r="M44" t="n">
         <v>516.0089179080152</v>
@@ -38079,7 +38079,7 @@
         <v>0</v>
       </c>
       <c r="P44" t="n">
-        <v>773.0000000000775</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
         <v>443.0293889420883</v>
@@ -38143,7 +38143,7 @@
         <v>312.2086062376757</v>
       </c>
       <c r="K45" t="n">
-        <v>230.4407630180518</v>
+        <v>378.1038546407913</v>
       </c>
       <c r="L45" t="n">
         <v>461.091375348687</v>
@@ -38152,7 +38152,7 @@
         <v>273.9500421645043</v>
       </c>
       <c r="N45" t="n">
-        <v>321.6265501086548</v>
+        <v>177.7614437006381</v>
       </c>
       <c r="O45" t="n">
         <v>428.4570219027464</v>
@@ -38219,7 +38219,7 @@
         <v>0</v>
       </c>
       <c r="J46" t="n">
-        <v>82.79148652211846</v>
+        <v>76.08171264277482</v>
       </c>
       <c r="K46" t="n">
         <v>0</v>
